--- a/outputs/供应链库存分析报告.xlsx
+++ b/outputs/供应链库存分析报告.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1-结论概览" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2-ABC分类" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3-ABC-XYZ矩阵" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="4-商品明细" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="5-履约诊断" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="1-结论概览" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="2-ABC分类" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="3-ABC-XYZ矩阵" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="4-商品明细" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="5-履约诊断" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -152,13 +152,13 @@
 </file>
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr/>
+          <a:p>
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -182,7 +182,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -222,8 +222,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:bodyPr/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -249,13 +249,13 @@
 </file>
 
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr/>
+          <a:p>
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -278,7 +278,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -306,7 +306,7 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>0</col>
@@ -321,9 +321,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+          <c:chart r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -343,9 +343,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+          <c:chart r:id="rId2"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -761,7 +761,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>13 个</t>
+          <t>9 个</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -778,7 +778,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>60 个</t>
+          <t>64 个</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -795,12 +795,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>1,782 件</t>
+          <t>1,922 件</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>95% 服务水平, Z=1.65</t>
+          <t>按 ABC 分档: A 99% / B 95% / C 90%</t>
         </is>
       </c>
     </row>
@@ -975,7 +975,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H9"/>
+  <dimension ref="A1:H8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -984,8 +984,8 @@
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="32" customWidth="1" min="8" max="8"/>
+    <col width="32" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1023,17 +1023,17 @@
       </c>
       <c r="F2" s="1" t="inlineStr">
         <is>
+          <t>销售额占比%</t>
+        </is>
+      </c>
+      <c r="G2" s="1" t="inlineStr">
+        <is>
+          <t>策略</t>
+        </is>
+      </c>
+      <c r="H2" s="1" t="inlineStr">
+        <is>
           <t>平均安全库存</t>
-        </is>
-      </c>
-      <c r="G2" s="1" t="inlineStr">
-        <is>
-          <t>销售额占比%</t>
-        </is>
-      </c>
-      <c r="H2" s="1" t="inlineStr">
-        <is>
-          <t>策略</t>
         </is>
       </c>
     </row>
@@ -1058,15 +1058,15 @@
         <v>0.353</v>
       </c>
       <c r="F3" t="n">
-        <v>91.94</v>
-      </c>
-      <c r="G3" t="n">
         <v>76.87</v>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>核心稳定品|JIT准时制,低安全库存,高频小批补货,盯周转</t>
         </is>
+      </c>
+      <c r="H3" t="n">
+        <v>129.61</v>
       </c>
     </row>
     <row r="4">
@@ -1081,24 +1081,24 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D4" t="n">
-        <v>4354478.87</v>
+        <v>4158076.58</v>
       </c>
       <c r="E4" t="n">
-        <v>0.178</v>
+        <v>0.356</v>
       </c>
       <c r="F4" t="n">
-        <v>74.33</v>
-      </c>
-      <c r="G4" t="n">
-        <v>11.84</v>
-      </c>
-      <c r="H4" t="inlineStr">
+        <v>11.3</v>
+      </c>
+      <c r="G4" t="inlineStr">
         <is>
           <t>常规稳定品|系统自动补货,经济订货批量EOQ</t>
         </is>
+      </c>
+      <c r="H4" t="n">
+        <v>120.24</v>
       </c>
     </row>
     <row r="5">
@@ -1122,15 +1122,15 @@
         <v>0.677</v>
       </c>
       <c r="F5" t="n">
-        <v>6.96</v>
-      </c>
-      <c r="G5" t="n">
         <v>0.5</v>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>常规波动品|定期review,适度安全库存</t>
         </is>
+      </c>
+      <c r="H5" t="n">
+        <v>6.94</v>
       </c>
     </row>
     <row r="6">
@@ -1145,24 +1145,24 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D6" t="n">
-        <v>2113038.81</v>
+        <v>2309441.1</v>
       </c>
       <c r="E6" t="n">
-        <v>4.692</v>
+        <v>4.666</v>
       </c>
       <c r="F6" t="n">
-        <v>30.28</v>
-      </c>
-      <c r="G6" t="n">
-        <v>5.74</v>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>常规高危品|提高安全库存或替换供应商/合并SKU</t>
-        </is>
+        <v>6.28</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>常规高危品|提高安全库存或考虑替换供应商/合并SKU</t>
+        </is>
+      </c>
+      <c r="H6" t="n">
+        <v>29.79</v>
       </c>
     </row>
     <row r="7">
@@ -1173,28 +1173,28 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>2</v>
+        <v>42</v>
       </c>
       <c r="D7" t="n">
-        <v>18692.06</v>
+        <v>1090914.27</v>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>0.702</v>
       </c>
       <c r="F7" t="n">
-        <v>29.32</v>
-      </c>
-      <c r="G7" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>长尾稳定品|简化管理,大批量低频次采购</t>
-        </is>
+        <v>2.97</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>长尾波动品|按订单采购,尽量降低持有</t>
+        </is>
+      </c>
+      <c r="H7" t="n">
+        <v>4.95</v>
       </c>
     </row>
     <row r="8">
@@ -1205,60 +1205,28 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>Z</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="D8" t="n">
-        <v>1090914.27</v>
+        <v>764394.09</v>
       </c>
       <c r="E8" t="n">
-        <v>0.702</v>
+        <v>3.626</v>
       </c>
       <c r="F8" t="n">
-        <v>6.37</v>
-      </c>
-      <c r="G8" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>长尾波动品|按订单采购,尽量降低持有</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Z</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
-        <v>51</v>
-      </c>
-      <c r="D9" t="n">
-        <v>745702.03</v>
-      </c>
-      <c r="E9" t="n">
-        <v>3.591</v>
-      </c>
-      <c r="F9" t="n">
-        <v>4.34</v>
-      </c>
-      <c r="G9" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="H9" t="inlineStr">
+        <v>2.08</v>
+      </c>
+      <c r="G8" t="inlineStr">
         <is>
           <t>长尾高危品|考虑淘汰/替代,避免占用资金与仓储</t>
         </is>
+      </c>
+      <c r="H8" t="n">
+        <v>4.11</v>
       </c>
     </row>
   </sheetData>
@@ -1272,15 +1240,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O120"/>
+  <dimension ref="A1:Q120"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="44" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
     <col width="10" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
@@ -1289,7 +1257,9 @@
     <col width="10" customWidth="1" min="12" max="12"/>
     <col width="10" customWidth="1" min="13" max="13"/>
     <col width="10" customWidth="1" min="14" max="14"/>
-    <col width="23" customWidth="1" min="15" max="15"/>
+    <col width="10" customWidth="1" min="15" max="15"/>
+    <col width="10" customWidth="1" min="16" max="16"/>
+    <col width="23" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1317,60 +1287,70 @@
       </c>
       <c r="D2" s="1" t="inlineStr">
         <is>
+          <t>服务水平%</t>
+        </is>
+      </c>
+      <c r="E2" s="1" t="inlineStr">
+        <is>
+          <t>Z值</t>
+        </is>
+      </c>
+      <c r="F2" s="1" t="inlineStr">
+        <is>
           <t>销售额</t>
         </is>
       </c>
-      <c r="E2" s="1" t="inlineStr">
+      <c r="G2" s="1" t="inlineStr">
         <is>
           <t>销量</t>
         </is>
       </c>
-      <c r="F2" s="1" t="inlineStr">
+      <c r="H2" s="1" t="inlineStr">
         <is>
           <t>订单数</t>
         </is>
       </c>
-      <c r="G2" s="1" t="inlineStr">
+      <c r="I2" s="1" t="inlineStr">
         <is>
           <t>均价</t>
         </is>
       </c>
-      <c r="H2" s="1" t="inlineStr">
+      <c r="J2" s="1" t="inlineStr">
         <is>
           <t>周需求均值</t>
         </is>
       </c>
-      <c r="I2" s="1" t="inlineStr">
+      <c r="K2" s="1" t="inlineStr">
         <is>
           <t>周需求标准差</t>
         </is>
       </c>
-      <c r="J2" s="1" t="inlineStr">
+      <c r="L2" s="1" t="inlineStr">
         <is>
           <t>CV</t>
         </is>
       </c>
-      <c r="K2" s="1" t="inlineStr">
+      <c r="M2" s="1" t="inlineStr">
         <is>
           <t>提前期_周</t>
         </is>
       </c>
-      <c r="L2" s="1" t="inlineStr">
+      <c r="N2" s="1" t="inlineStr">
         <is>
           <t>安全库存</t>
         </is>
       </c>
-      <c r="M2" s="1" t="inlineStr">
+      <c r="O2" s="1" t="inlineStr">
         <is>
           <t>再订货点</t>
         </is>
       </c>
-      <c r="N2" s="1" t="inlineStr">
+      <c r="P2" s="1" t="inlineStr">
         <is>
           <t>延期率</t>
         </is>
       </c>
-      <c r="O2" s="1" t="inlineStr">
+      <c r="Q2" s="1" t="inlineStr">
         <is>
           <t>品类</t>
         </is>
@@ -1393,39 +1373,45 @@
         </is>
       </c>
       <c r="D3" t="n">
+        <v>99</v>
+      </c>
+      <c r="E3" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="F3" t="n">
         <v>6929653.69</v>
       </c>
-      <c r="E3" t="n">
+      <c r="G3" t="n">
         <v>17325</v>
       </c>
-      <c r="F3" t="n">
+      <c r="H3" t="n">
         <v>15164</v>
       </c>
-      <c r="G3" t="n">
+      <c r="I3" t="n">
         <v>399.98</v>
       </c>
-      <c r="H3" t="n">
+      <c r="J3" t="n">
         <v>106.94</v>
       </c>
-      <c r="I3" t="n">
+      <c r="K3" t="n">
         <v>39.72</v>
       </c>
-      <c r="J3" t="n">
+      <c r="L3" t="n">
         <v>0.35</v>
       </c>
-      <c r="K3" t="n">
+      <c r="M3" t="n">
         <v>0.5</v>
       </c>
-      <c r="L3" t="n">
-        <v>46.34</v>
-      </c>
-      <c r="M3" t="n">
-        <v>99.81</v>
-      </c>
       <c r="N3" t="n">
+        <v>65.33</v>
+      </c>
+      <c r="O3" t="n">
+        <v>118.8</v>
+      </c>
+      <c r="P3" t="n">
         <v>57.32</v>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
         <is>
           <t>Fishing</t>
         </is>
@@ -1448,39 +1434,45 @@
         </is>
       </c>
       <c r="D4" t="n">
+        <v>99</v>
+      </c>
+      <c r="E4" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="F4" t="n">
         <v>4421143.14</v>
       </c>
-      <c r="E4" t="n">
+      <c r="G4" t="n">
         <v>73698</v>
       </c>
-      <c r="F4" t="n">
+      <c r="H4" t="n">
         <v>20359</v>
       </c>
-      <c r="G4" t="n">
+      <c r="I4" t="n">
         <v>59.99</v>
       </c>
-      <c r="H4" t="n">
+      <c r="J4" t="n">
         <v>454.93</v>
       </c>
-      <c r="I4" t="n">
+      <c r="K4" t="n">
         <v>165.98</v>
       </c>
-      <c r="J4" t="n">
+      <c r="L4" t="n">
         <v>0.35</v>
       </c>
-      <c r="K4" t="n">
+      <c r="M4" t="n">
         <v>0.5</v>
       </c>
-      <c r="L4" t="n">
-        <v>193.92</v>
-      </c>
-      <c r="M4" t="n">
-        <v>422.02</v>
-      </c>
       <c r="N4" t="n">
+        <v>273.37</v>
+      </c>
+      <c r="O4" t="n">
+        <v>501.47</v>
+      </c>
+      <c r="P4" t="n">
         <v>57.32</v>
       </c>
-      <c r="O4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
         <is>
           <t>Cleats</t>
         </is>
@@ -1503,39 +1495,45 @@
         </is>
       </c>
       <c r="D5" t="n">
+        <v>99</v>
+      </c>
+      <c r="E5" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="F5" t="n">
         <v>4118425.57</v>
       </c>
-      <c r="E5" t="n">
+      <c r="G5" t="n">
         <v>13729</v>
       </c>
-      <c r="F5" t="n">
+      <c r="H5" t="n">
         <v>12299</v>
       </c>
-      <c r="G5" t="n">
+      <c r="I5" t="n">
         <v>299.98</v>
       </c>
-      <c r="H5" t="n">
+      <c r="J5" t="n">
         <v>84.75</v>
       </c>
-      <c r="I5" t="n">
+      <c r="K5" t="n">
         <v>31.17</v>
       </c>
-      <c r="J5" t="n">
+      <c r="L5" t="n">
         <v>0.35</v>
       </c>
-      <c r="K5" t="n">
+      <c r="M5" t="n">
         <v>0.5</v>
       </c>
-      <c r="L5" t="n">
-        <v>36.37</v>
-      </c>
-      <c r="M5" t="n">
-        <v>78.73999999999999</v>
-      </c>
       <c r="N5" t="n">
+        <v>51.27</v>
+      </c>
+      <c r="O5" t="n">
+        <v>93.65000000000001</v>
+      </c>
+      <c r="P5" t="n">
         <v>56.9</v>
       </c>
-      <c r="O5" t="inlineStr">
+      <c r="Q5" t="inlineStr">
         <is>
           <t>Camping &amp; Hiking</t>
         </is>
@@ -1558,39 +1556,45 @@
         </is>
       </c>
       <c r="D6" t="n">
+        <v>99</v>
+      </c>
+      <c r="E6" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="F6" t="n">
         <v>3667633.2</v>
       </c>
-      <c r="E6" t="n">
+      <c r="G6" t="n">
         <v>36680</v>
       </c>
-      <c r="F6" t="n">
+      <c r="H6" t="n">
         <v>11092</v>
       </c>
-      <c r="G6" t="n">
+      <c r="I6" t="n">
         <v>99.98999999999999</v>
       </c>
-      <c r="H6" t="n">
+      <c r="J6" t="n">
         <v>226.42</v>
       </c>
-      <c r="I6" t="n">
+      <c r="K6" t="n">
         <v>85</v>
       </c>
-      <c r="J6" t="n">
+      <c r="L6" t="n">
         <v>0.36</v>
       </c>
-      <c r="K6" t="n">
+      <c r="M6" t="n">
         <v>0.5</v>
       </c>
-      <c r="L6" t="n">
-        <v>99.03</v>
-      </c>
-      <c r="M6" t="n">
-        <v>211.92</v>
-      </c>
       <c r="N6" t="n">
+        <v>139.61</v>
+      </c>
+      <c r="O6" t="n">
+        <v>252.5</v>
+      </c>
+      <c r="P6" t="n">
         <v>56.91</v>
       </c>
-      <c r="O6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
         <is>
           <t>Cardio Equipment</t>
         </is>
@@ -1613,39 +1617,45 @@
         </is>
       </c>
       <c r="D7" t="n">
+        <v>99</v>
+      </c>
+      <c r="E7" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="F7" t="n">
         <v>3147800</v>
       </c>
-      <c r="E7" t="n">
+      <c r="G7" t="n">
         <v>62956</v>
       </c>
-      <c r="F7" t="n">
+      <c r="H7" t="n">
         <v>17869</v>
       </c>
-      <c r="G7" t="n">
+      <c r="I7" t="n">
         <v>50</v>
       </c>
-      <c r="H7" t="n">
+      <c r="J7" t="n">
         <v>388.62</v>
       </c>
-      <c r="I7" t="n">
+      <c r="K7" t="n">
         <v>143.82</v>
       </c>
-      <c r="J7" t="n">
+      <c r="L7" t="n">
         <v>0.35</v>
       </c>
-      <c r="K7" t="n">
+      <c r="M7" t="n">
         <v>0.5</v>
       </c>
-      <c r="L7" t="n">
-        <v>167.31</v>
-      </c>
-      <c r="M7" t="n">
-        <v>360.49</v>
-      </c>
       <c r="N7" t="n">
+        <v>235.86</v>
+      </c>
+      <c r="O7" t="n">
+        <v>429.04</v>
+      </c>
+      <c r="P7" t="n">
         <v>57.13</v>
       </c>
-      <c r="O7" t="inlineStr">
+      <c r="Q7" t="inlineStr">
         <is>
           <t>Women's Apparel</t>
         </is>
@@ -1668,39 +1678,45 @@
         </is>
       </c>
       <c r="D8" t="n">
+        <v>99</v>
+      </c>
+      <c r="E8" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="F8" t="n">
         <v>3099845.09</v>
       </c>
-      <c r="E8" t="n">
+      <c r="G8" t="n">
         <v>15500</v>
       </c>
-      <c r="F8" t="n">
+      <c r="H8" t="n">
         <v>13727</v>
       </c>
-      <c r="G8" t="n">
+      <c r="I8" t="n">
         <v>199.99</v>
       </c>
-      <c r="H8" t="n">
+      <c r="J8" t="n">
         <v>95.68000000000001</v>
       </c>
-      <c r="I8" t="n">
+      <c r="K8" t="n">
         <v>35.51</v>
       </c>
-      <c r="J8" t="n">
+      <c r="L8" t="n">
         <v>0.35</v>
       </c>
-      <c r="K8" t="n">
+      <c r="M8" t="n">
         <v>0.5</v>
       </c>
-      <c r="L8" t="n">
-        <v>41.31</v>
-      </c>
-      <c r="M8" t="n">
-        <v>88.87</v>
-      </c>
       <c r="N8" t="n">
+        <v>58.23</v>
+      </c>
+      <c r="O8" t="n">
+        <v>105.79</v>
+      </c>
+      <c r="P8" t="n">
         <v>57.2</v>
       </c>
-      <c r="O8" t="inlineStr">
+      <c r="Q8" t="inlineStr">
         <is>
           <t>Water Sports</t>
         </is>
@@ -1723,39 +1739,45 @@
         </is>
       </c>
       <c r="D9" t="n">
+        <v>99</v>
+      </c>
+      <c r="E9" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="F9" t="n">
         <v>2891757.66</v>
       </c>
-      <c r="E9" t="n">
+      <c r="G9" t="n">
         <v>22246</v>
       </c>
-      <c r="F9" t="n">
+      <c r="H9" t="n">
         <v>18783</v>
       </c>
-      <c r="G9" t="n">
+      <c r="I9" t="n">
         <v>129.99</v>
       </c>
-      <c r="H9" t="n">
+      <c r="J9" t="n">
         <v>137.32</v>
       </c>
-      <c r="I9" t="n">
+      <c r="K9" t="n">
         <v>50.82</v>
       </c>
-      <c r="J9" t="n">
+      <c r="L9" t="n">
         <v>0.35</v>
       </c>
-      <c r="K9" t="n">
+      <c r="M9" t="n">
         <v>0.5</v>
       </c>
-      <c r="L9" t="n">
-        <v>59.29</v>
-      </c>
-      <c r="M9" t="n">
-        <v>127.95</v>
-      </c>
       <c r="N9" t="n">
+        <v>83.59</v>
+      </c>
+      <c r="O9" t="n">
+        <v>152.25</v>
+      </c>
+      <c r="P9" t="n">
         <v>56.93</v>
       </c>
-      <c r="O9" t="inlineStr">
+      <c r="Q9" t="inlineStr">
         <is>
           <t>Men's Footwear</t>
         </is>
@@ -1778,39 +1800,45 @@
         </is>
       </c>
       <c r="D10" t="n">
+        <v>95</v>
+      </c>
+      <c r="E10" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="F10" t="n">
         <v>2888993.91</v>
       </c>
-      <c r="E10" t="n">
+      <c r="G10" t="n">
         <v>57803</v>
       </c>
-      <c r="F10" t="n">
+      <c r="H10" t="n">
         <v>16623</v>
       </c>
-      <c r="G10" t="n">
+      <c r="I10" t="n">
         <v>49.98</v>
       </c>
-      <c r="H10" t="n">
+      <c r="J10" t="n">
         <v>356.81</v>
       </c>
-      <c r="I10" t="n">
+      <c r="K10" t="n">
         <v>132.61</v>
       </c>
-      <c r="J10" t="n">
+      <c r="L10" t="n">
         <v>0.36</v>
       </c>
-      <c r="K10" t="n">
+      <c r="M10" t="n">
         <v>0.5</v>
       </c>
-      <c r="L10" t="n">
-        <v>154.72</v>
-      </c>
-      <c r="M10" t="n">
-        <v>333.12</v>
-      </c>
       <c r="N10" t="n">
+        <v>154.25</v>
+      </c>
+      <c r="O10" t="n">
+        <v>332.66</v>
+      </c>
+      <c r="P10" t="n">
         <v>57.22</v>
       </c>
-      <c r="O10" t="inlineStr">
+      <c r="Q10" t="inlineStr">
         <is>
           <t>Indoor/Outdoor Games</t>
         </is>
@@ -1833,39 +1861,45 @@
         </is>
       </c>
       <c r="D11" t="n">
+        <v>95</v>
+      </c>
+      <c r="E11" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="F11" t="n">
         <v>1269082.67</v>
       </c>
-      <c r="E11" t="n">
+      <c r="G11" t="n">
         <v>31735</v>
       </c>
-      <c r="F11" t="n">
+      <c r="H11" t="n">
         <v>9825</v>
       </c>
-      <c r="G11" t="n">
+      <c r="I11" t="n">
         <v>39.99</v>
       </c>
-      <c r="H11" t="n">
+      <c r="J11" t="n">
         <v>195.9</v>
       </c>
-      <c r="I11" t="n">
+      <c r="K11" t="n">
         <v>74.23</v>
       </c>
-      <c r="J11" t="n">
+      <c r="L11" t="n">
         <v>0.36</v>
       </c>
-      <c r="K11" t="n">
+      <c r="M11" t="n">
         <v>0.5</v>
       </c>
-      <c r="L11" t="n">
-        <v>86.48</v>
-      </c>
-      <c r="M11" t="n">
-        <v>184.16</v>
-      </c>
       <c r="N11" t="n">
+        <v>86.22</v>
+      </c>
+      <c r="O11" t="n">
+        <v>183.9</v>
+      </c>
+      <c r="P11" t="n">
         <v>57.7</v>
       </c>
-      <c r="O11" t="inlineStr">
+      <c r="Q11" t="inlineStr">
         <is>
           <t>Shop By Sport</t>
         </is>
@@ -1888,39 +1922,45 @@
         </is>
       </c>
       <c r="D12" t="n">
+        <v>95</v>
+      </c>
+      <c r="E12" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="F12" t="n">
         <v>663000</v>
       </c>
-      <c r="E12" t="n">
+      <c r="G12" t="n">
         <v>442</v>
       </c>
-      <c r="F12" t="n">
+      <c r="H12" t="n">
         <v>442</v>
       </c>
-      <c r="G12" t="n">
+      <c r="I12" t="n">
         <v>1500</v>
       </c>
-      <c r="H12" t="n">
+      <c r="J12" t="n">
         <v>2.73</v>
       </c>
-      <c r="I12" t="n">
+      <c r="K12" t="n">
         <v>22.79</v>
       </c>
-      <c r="J12" t="n">
+      <c r="L12" t="n">
         <v>4.95</v>
       </c>
-      <c r="K12" t="n">
+      <c r="M12" t="n">
         <v>0.52</v>
       </c>
-      <c r="L12" t="n">
-        <v>27.04</v>
-      </c>
-      <c r="M12" t="n">
-        <v>28.45</v>
-      </c>
       <c r="N12" t="n">
+        <v>26.96</v>
+      </c>
+      <c r="O12" t="n">
+        <v>28.37</v>
+      </c>
+      <c r="P12" t="n">
         <v>52.71</v>
       </c>
-      <c r="O12" t="inlineStr">
+      <c r="Q12" t="inlineStr">
         <is>
           <t>Computers</t>
         </is>
@@ -1943,39 +1983,45 @@
         </is>
       </c>
       <c r="D13" t="n">
+        <v>95</v>
+      </c>
+      <c r="E13" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="F13" t="n">
         <v>267607.69</v>
       </c>
-      <c r="E13" t="n">
+      <c r="G13" t="n">
         <v>592</v>
       </c>
-      <c r="F13" t="n">
+      <c r="H13" t="n">
         <v>592</v>
       </c>
-      <c r="G13" t="n">
+      <c r="I13" t="n">
         <v>452.04</v>
       </c>
-      <c r="H13" t="n">
+      <c r="J13" t="n">
         <v>3.65</v>
       </c>
-      <c r="I13" t="n">
+      <c r="K13" t="n">
         <v>34.24</v>
       </c>
-      <c r="J13" t="n">
+      <c r="L13" t="n">
         <v>5.91</v>
       </c>
-      <c r="K13" t="n">
+      <c r="M13" t="n">
         <v>0.48</v>
       </c>
-      <c r="L13" t="n">
-        <v>39.02</v>
-      </c>
-      <c r="M13" t="n">
-        <v>40.76</v>
-      </c>
       <c r="N13" t="n">
+        <v>38.9</v>
+      </c>
+      <c r="O13" t="n">
+        <v>40.64</v>
+      </c>
+      <c r="P13" t="n">
         <v>61.99</v>
       </c>
-      <c r="O13" t="inlineStr">
+      <c r="Q13" t="inlineStr">
         <is>
           <t>Cameras</t>
         </is>
@@ -1998,39 +2044,45 @@
         </is>
       </c>
       <c r="D14" t="n">
+        <v>95</v>
+      </c>
+      <c r="E14" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="F14" t="n">
         <v>257768.73</v>
       </c>
-      <c r="E14" t="n">
+      <c r="G14" t="n">
         <v>484</v>
       </c>
-      <c r="F14" t="n">
+      <c r="H14" t="n">
         <v>484</v>
       </c>
-      <c r="G14" t="n">
+      <c r="I14" t="n">
         <v>532.58</v>
       </c>
-      <c r="H14" t="n">
+      <c r="J14" t="n">
         <v>2.99</v>
       </c>
-      <c r="I14" t="n">
+      <c r="K14" t="n">
         <v>31.36</v>
       </c>
-      <c r="J14" t="n">
+      <c r="L14" t="n">
         <v>4.99</v>
       </c>
-      <c r="K14" t="n">
+      <c r="M14" t="n">
         <v>0.5</v>
       </c>
-      <c r="L14" t="n">
-        <v>36.59</v>
-      </c>
-      <c r="M14" t="n">
-        <v>38.08</v>
-      </c>
       <c r="N14" t="n">
+        <v>36.48</v>
+      </c>
+      <c r="O14" t="n">
+        <v>37.97</v>
+      </c>
+      <c r="P14" t="n">
         <v>57.02</v>
       </c>
-      <c r="O14" t="inlineStr">
+      <c r="Q14" t="inlineStr">
         <is>
           <t>Garden</t>
         </is>
@@ -2053,39 +2105,45 @@
         </is>
       </c>
       <c r="D15" t="n">
+        <v>95</v>
+      </c>
+      <c r="E15" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="F15" t="n">
         <v>232829.2</v>
       </c>
-      <c r="E15" t="n">
+      <c r="G15" t="n">
         <v>652</v>
       </c>
-      <c r="F15" t="n">
+      <c r="H15" t="n">
         <v>652</v>
       </c>
-      <c r="G15" t="n">
+      <c r="I15" t="n">
         <v>357.1</v>
       </c>
-      <c r="H15" t="n">
+      <c r="J15" t="n">
         <v>4.02</v>
       </c>
-      <c r="I15" t="n">
+      <c r="K15" t="n">
         <v>30.97</v>
       </c>
-      <c r="J15" t="n">
+      <c r="L15" t="n">
         <v>4.99</v>
       </c>
-      <c r="K15" t="n">
+      <c r="M15" t="n">
         <v>0.52</v>
       </c>
-      <c r="L15" t="n">
-        <v>36.7</v>
-      </c>
-      <c r="M15" t="n">
-        <v>38.77</v>
-      </c>
       <c r="N15" t="n">
+        <v>36.59</v>
+      </c>
+      <c r="O15" t="n">
+        <v>38.66</v>
+      </c>
+      <c r="P15" t="n">
         <v>56.6</v>
       </c>
-      <c r="O15" t="inlineStr">
+      <c r="Q15" t="inlineStr">
         <is>
           <t>Children's Clothing</t>
         </is>
@@ -2108,39 +2166,45 @@
         </is>
       </c>
       <c r="D16" t="n">
+        <v>95</v>
+      </c>
+      <c r="E16" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="F16" t="n">
         <v>223356.33</v>
       </c>
-      <c r="E16" t="n">
+      <c r="G16" t="n">
         <v>484</v>
       </c>
-      <c r="F16" t="n">
+      <c r="H16" t="n">
         <v>484</v>
       </c>
-      <c r="G16" t="n">
+      <c r="I16" t="n">
         <v>461.48</v>
       </c>
-      <c r="H16" t="n">
+      <c r="J16" t="n">
         <v>2.99</v>
       </c>
-      <c r="I16" t="n">
+      <c r="K16" t="n">
         <v>23.56</v>
       </c>
-      <c r="J16" t="n">
+      <c r="L16" t="n">
         <v>4.25</v>
       </c>
-      <c r="K16" t="n">
+      <c r="M16" t="n">
         <v>0.51</v>
       </c>
-      <c r="L16" t="n">
-        <v>27.8</v>
-      </c>
-      <c r="M16" t="n">
-        <v>29.33</v>
-      </c>
       <c r="N16" t="n">
+        <v>27.72</v>
+      </c>
+      <c r="O16" t="n">
+        <v>29.25</v>
+      </c>
+      <c r="P16" t="n">
         <v>59.5</v>
       </c>
-      <c r="O16" t="inlineStr">
+      <c r="Q16" t="inlineStr">
         <is>
           <t>Crafts</t>
         </is>
@@ -2163,39 +2227,45 @@
         </is>
       </c>
       <c r="D17" t="n">
+        <v>95</v>
+      </c>
+      <c r="E17" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="F17" t="n">
         <v>140283</v>
       </c>
-      <c r="E17" t="n">
+      <c r="G17" t="n">
         <v>650</v>
       </c>
-      <c r="F17" t="n">
+      <c r="H17" t="n">
         <v>650</v>
       </c>
-      <c r="G17" t="n">
+      <c r="I17" t="n">
         <v>215.82</v>
       </c>
-      <c r="H17" t="n">
+      <c r="J17" t="n">
         <v>4.01</v>
       </c>
-      <c r="I17" t="n">
+      <c r="K17" t="n">
         <v>29.82</v>
       </c>
-      <c r="J17" t="n">
+      <c r="L17" t="n">
         <v>4.3</v>
       </c>
-      <c r="K17" t="n">
+      <c r="M17" t="n">
         <v>0.51</v>
       </c>
-      <c r="L17" t="n">
-        <v>34.99</v>
-      </c>
-      <c r="M17" t="n">
-        <v>37.02</v>
-      </c>
       <c r="N17" t="n">
+        <v>34.88</v>
+      </c>
+      <c r="O17" t="n">
+        <v>36.91</v>
+      </c>
+      <c r="P17" t="n">
         <v>58.62</v>
       </c>
-      <c r="O17" t="inlineStr">
+      <c r="Q17" t="inlineStr">
         <is>
           <t>Women's Clothing</t>
         </is>
@@ -2214,43 +2284,49 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>Z</t>
         </is>
       </c>
       <c r="D18" t="n">
+        <v>95</v>
+      </c>
+      <c r="E18" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="F18" t="n">
         <v>117006.75</v>
       </c>
-      <c r="E18" t="n">
+      <c r="G18" t="n">
         <v>357</v>
       </c>
-      <c r="F18" t="n">
+      <c r="H18" t="n">
         <v>357</v>
       </c>
-      <c r="G18" t="n">
+      <c r="I18" t="n">
         <v>327.75</v>
       </c>
-      <c r="H18" t="n">
+      <c r="J18" t="n">
         <v>2.2</v>
       </c>
-      <c r="I18" t="n">
+      <c r="K18" t="n">
         <v>18.43</v>
       </c>
-      <c r="J18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" t="n">
+      <c r="L18" t="n">
+        <v>4.32</v>
+      </c>
+      <c r="M18" t="n">
         <v>0.5</v>
       </c>
-      <c r="L18" t="n">
-        <v>21.47</v>
-      </c>
-      <c r="M18" t="n">
-        <v>22.57</v>
-      </c>
       <c r="N18" t="n">
+        <v>21.41</v>
+      </c>
+      <c r="O18" t="n">
+        <v>22.51</v>
+      </c>
+      <c r="P18" t="n">
         <v>59.94</v>
       </c>
-      <c r="O18" t="inlineStr">
+      <c r="Q18" t="inlineStr">
         <is>
           <t>Sporting Goods</t>
         </is>
@@ -2273,39 +2349,45 @@
         </is>
       </c>
       <c r="D19" t="n">
+        <v>95</v>
+      </c>
+      <c r="E19" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="F19" t="n">
         <v>113122.1</v>
       </c>
-      <c r="E19" t="n">
+      <c r="G19" t="n">
         <v>434</v>
       </c>
-      <c r="F19" t="n">
+      <c r="H19" t="n">
         <v>434</v>
       </c>
-      <c r="G19" t="n">
+      <c r="I19" t="n">
         <v>260.65</v>
       </c>
-      <c r="H19" t="n">
+      <c r="J19" t="n">
         <v>2.68</v>
       </c>
-      <c r="I19" t="n">
+      <c r="K19" t="n">
         <v>19.57</v>
       </c>
-      <c r="J19" t="n">
+      <c r="L19" t="n">
         <v>4.49</v>
       </c>
-      <c r="K19" t="n">
+      <c r="M19" t="n">
         <v>0.5</v>
       </c>
-      <c r="L19" t="n">
-        <v>22.77</v>
-      </c>
-      <c r="M19" t="n">
-        <v>24.1</v>
-      </c>
       <c r="N19" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="O19" t="n">
+        <v>24.03</v>
+      </c>
+      <c r="P19" t="n">
         <v>59.45</v>
       </c>
-      <c r="O19" t="inlineStr">
+      <c r="Q19" t="inlineStr">
         <is>
           <t>Music</t>
         </is>
@@ -2328,39 +2410,45 @@
         </is>
       </c>
       <c r="D20" t="n">
+        <v>95</v>
+      </c>
+      <c r="E20" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="F20" t="n">
         <v>108991.28</v>
       </c>
-      <c r="E20" t="n">
+      <c r="G20" t="n">
         <v>431</v>
       </c>
-      <c r="F20" t="n">
+      <c r="H20" t="n">
         <v>431</v>
       </c>
-      <c r="G20" t="n">
+      <c r="I20" t="n">
         <v>252.88</v>
       </c>
-      <c r="H20" t="n">
+      <c r="J20" t="n">
         <v>2.66</v>
       </c>
-      <c r="I20" t="n">
+      <c r="K20" t="n">
         <v>24.26</v>
       </c>
-      <c r="J20" t="n">
+      <c r="L20" t="n">
         <v>3.9</v>
       </c>
-      <c r="K20" t="n">
+      <c r="M20" t="n">
         <v>0.49</v>
       </c>
-      <c r="L20" t="n">
-        <v>28.02</v>
-      </c>
-      <c r="M20" t="n">
-        <v>29.32</v>
-      </c>
       <c r="N20" t="n">
+        <v>27.94</v>
+      </c>
+      <c r="O20" t="n">
+        <v>29.24</v>
+      </c>
+      <c r="P20" t="n">
         <v>59.16</v>
       </c>
-      <c r="O20" t="inlineStr">
+      <c r="Q20" t="inlineStr">
         <is>
           <t>Consumer Electronics</t>
         </is>
@@ -2383,39 +2471,45 @@
         </is>
       </c>
       <c r="D21" t="n">
+        <v>95</v>
+      </c>
+      <c r="E21" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="F21" t="n">
         <v>106080.48</v>
       </c>
-      <c r="E21" t="n">
+      <c r="G21" t="n">
         <v>362</v>
       </c>
-      <c r="F21" t="n">
+      <c r="H21" t="n">
         <v>362</v>
       </c>
-      <c r="G21" t="n">
+      <c r="I21" t="n">
         <v>293.04</v>
       </c>
-      <c r="H21" t="n">
+      <c r="J21" t="n">
         <v>2.23</v>
       </c>
-      <c r="I21" t="n">
+      <c r="K21" t="n">
         <v>16.9</v>
       </c>
-      <c r="J21" t="n">
+      <c r="L21" t="n">
         <v>4.47</v>
       </c>
-      <c r="K21" t="n">
+      <c r="M21" t="n">
         <v>0.49</v>
       </c>
-      <c r="L21" t="n">
-        <v>19.6</v>
-      </c>
-      <c r="M21" t="n">
-        <v>20.7</v>
-      </c>
       <c r="N21" t="n">
+        <v>19.55</v>
+      </c>
+      <c r="O21" t="n">
+        <v>20.65</v>
+      </c>
+      <c r="P21" t="n">
         <v>58.56</v>
       </c>
-      <c r="O21" t="inlineStr">
+      <c r="Q21" t="inlineStr">
         <is>
           <t>Health and Beauty</t>
         </is>
@@ -2434,43 +2528,49 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>Z</t>
         </is>
       </c>
       <c r="D22" t="n">
+        <v>95</v>
+      </c>
+      <c r="E22" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="F22" t="n">
         <v>79395.53999999999</v>
       </c>
-      <c r="E22" t="n">
+      <c r="G22" t="n">
         <v>483</v>
       </c>
-      <c r="F22" t="n">
+      <c r="H22" t="n">
         <v>483</v>
       </c>
-      <c r="G22" t="n">
+      <c r="I22" t="n">
         <v>164.38</v>
       </c>
-      <c r="H22" t="n">
+      <c r="J22" t="n">
         <v>2.98</v>
       </c>
-      <c r="I22" t="n">
+      <c r="K22" t="n">
         <v>29.13</v>
       </c>
-      <c r="J22" t="n">
-        <v>0</v>
-      </c>
-      <c r="K22" t="n">
+      <c r="L22" t="n">
+        <v>4.78</v>
+      </c>
+      <c r="M22" t="n">
         <v>0.52</v>
       </c>
-      <c r="L22" t="n">
-        <v>34.66</v>
-      </c>
-      <c r="M22" t="n">
-        <v>36.21</v>
-      </c>
       <c r="N22" t="n">
+        <v>34.55</v>
+      </c>
+      <c r="O22" t="n">
+        <v>36.1</v>
+      </c>
+      <c r="P22" t="n">
         <v>56.31</v>
       </c>
-      <c r="O22" t="inlineStr">
+      <c r="Q22" t="inlineStr">
         <is>
           <t>DVDs</t>
         </is>
@@ -2493,39 +2593,45 @@
         </is>
       </c>
       <c r="D23" t="n">
+        <v>95</v>
+      </c>
+      <c r="E23" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="F23" t="n">
         <v>67830</v>
       </c>
-      <c r="E23" t="n">
+      <c r="G23" t="n">
         <v>969</v>
       </c>
-      <c r="F23" t="n">
+      <c r="H23" t="n">
         <v>313</v>
       </c>
-      <c r="G23" t="n">
+      <c r="I23" t="n">
         <v>70</v>
       </c>
-      <c r="H23" t="n">
+      <c r="J23" t="n">
         <v>5.98</v>
       </c>
-      <c r="I23" t="n">
+      <c r="K23" t="n">
         <v>5.86</v>
       </c>
-      <c r="J23" t="n">
+      <c r="L23" t="n">
         <v>0.66</v>
       </c>
-      <c r="K23" t="n">
+      <c r="M23" t="n">
         <v>0.49</v>
       </c>
-      <c r="L23" t="n">
-        <v>6.78</v>
-      </c>
-      <c r="M23" t="n">
-        <v>9.720000000000001</v>
-      </c>
       <c r="N23" t="n">
+        <v>6.76</v>
+      </c>
+      <c r="O23" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="P23" t="n">
         <v>55.1</v>
       </c>
-      <c r="O23" t="inlineStr">
+      <c r="Q23" t="inlineStr">
         <is>
           <t>Girls' Apparel</t>
         </is>
@@ -2548,39 +2654,45 @@
         </is>
       </c>
       <c r="D24" t="n">
+        <v>95</v>
+      </c>
+      <c r="E24" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="F24" t="n">
         <v>61490</v>
       </c>
-      <c r="E24" t="n">
+      <c r="G24" t="n">
         <v>946</v>
       </c>
-      <c r="F24" t="n">
+      <c r="H24" t="n">
         <v>309</v>
       </c>
-      <c r="G24" t="n">
+      <c r="I24" t="n">
         <v>65</v>
       </c>
-      <c r="H24" t="n">
+      <c r="J24" t="n">
         <v>5.84</v>
       </c>
-      <c r="I24" t="n">
+      <c r="K24" t="n">
         <v>5.83</v>
       </c>
-      <c r="J24" t="n">
+      <c r="L24" t="n">
         <v>0.6899999999999999</v>
       </c>
-      <c r="K24" t="n">
+      <c r="M24" t="n">
         <v>0.5</v>
       </c>
-      <c r="L24" t="n">
-        <v>6.82</v>
-      </c>
-      <c r="M24" t="n">
-        <v>9.76</v>
-      </c>
       <c r="N24" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="O24" t="n">
+        <v>9.74</v>
+      </c>
+      <c r="P24" t="n">
         <v>58.9</v>
       </c>
-      <c r="O24" t="inlineStr">
+      <c r="Q24" t="inlineStr">
         <is>
           <t>Golf Shoes</t>
         </is>
@@ -2603,39 +2715,45 @@
         </is>
       </c>
       <c r="D25" t="n">
+        <v>95</v>
+      </c>
+      <c r="E25" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="F25" t="n">
         <v>56330.61</v>
       </c>
-      <c r="E25" t="n">
+      <c r="G25" t="n">
         <v>939</v>
       </c>
-      <c r="F25" t="n">
+      <c r="H25" t="n">
         <v>303</v>
       </c>
-      <c r="G25" t="n">
+      <c r="I25" t="n">
         <v>59.99</v>
       </c>
-      <c r="H25" t="n">
+      <c r="J25" t="n">
         <v>5.8</v>
       </c>
-      <c r="I25" t="n">
+      <c r="K25" t="n">
         <v>6.24</v>
       </c>
-      <c r="J25" t="n">
+      <c r="L25" t="n">
         <v>0.6899999999999999</v>
       </c>
-      <c r="K25" t="n">
+      <c r="M25" t="n">
         <v>0.5</v>
       </c>
-      <c r="L25" t="n">
-        <v>7.29</v>
-      </c>
-      <c r="M25" t="n">
-        <v>10.2</v>
-      </c>
       <c r="N25" t="n">
+        <v>7.27</v>
+      </c>
+      <c r="O25" t="n">
+        <v>10.18</v>
+      </c>
+      <c r="P25" t="n">
         <v>52.13</v>
       </c>
-      <c r="O25" t="inlineStr">
+      <c r="Q25" t="inlineStr">
         <is>
           <t>Baseball &amp; Softball</t>
         </is>
@@ -2658,39 +2776,45 @@
         </is>
       </c>
       <c r="D26" t="n">
+        <v>90</v>
+      </c>
+      <c r="E26" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="F26" t="n">
         <v>47206.92</v>
       </c>
-      <c r="E26" t="n">
+      <c r="G26" t="n">
         <v>908</v>
       </c>
-      <c r="F26" t="n">
+      <c r="H26" t="n">
         <v>305</v>
       </c>
-      <c r="G26" t="n">
+      <c r="I26" t="n">
         <v>51.99</v>
       </c>
-      <c r="H26" t="n">
+      <c r="J26" t="n">
         <v>5.6</v>
       </c>
-      <c r="I26" t="n">
+      <c r="K26" t="n">
         <v>5.94</v>
       </c>
-      <c r="J26" t="n">
+      <c r="L26" t="n">
         <v>0.73</v>
       </c>
-      <c r="K26" t="n">
+      <c r="M26" t="n">
         <v>0.49</v>
       </c>
-      <c r="L26" t="n">
-        <v>6.87</v>
-      </c>
-      <c r="M26" t="n">
-        <v>9.619999999999999</v>
-      </c>
       <c r="N26" t="n">
+        <v>5.34</v>
+      </c>
+      <c r="O26" t="n">
+        <v>8.09</v>
+      </c>
+      <c r="P26" t="n">
         <v>57.52</v>
       </c>
-      <c r="O26" t="inlineStr">
+      <c r="Q26" t="inlineStr">
         <is>
           <t>Electronics</t>
         </is>
@@ -2713,39 +2837,45 @@
         </is>
       </c>
       <c r="D27" t="n">
+        <v>90</v>
+      </c>
+      <c r="E27" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="F27" t="n">
         <v>46559.59</v>
       </c>
-      <c r="E27" t="n">
+      <c r="G27" t="n">
         <v>847</v>
       </c>
-      <c r="F27" t="n">
+      <c r="H27" t="n">
         <v>286</v>
       </c>
-      <c r="G27" t="n">
+      <c r="I27" t="n">
         <v>54.97</v>
       </c>
-      <c r="H27" t="n">
+      <c r="J27" t="n">
         <v>5.23</v>
       </c>
-      <c r="I27" t="n">
+      <c r="K27" t="n">
         <v>5.66</v>
       </c>
-      <c r="J27" t="n">
+      <c r="L27" t="n">
         <v>0.7</v>
       </c>
-      <c r="K27" t="n">
+      <c r="M27" t="n">
         <v>0.49</v>
       </c>
-      <c r="L27" t="n">
-        <v>6.56</v>
-      </c>
-      <c r="M27" t="n">
-        <v>9.140000000000001</v>
-      </c>
       <c r="N27" t="n">
+        <v>5.09</v>
+      </c>
+      <c r="O27" t="n">
+        <v>7.67</v>
+      </c>
+      <c r="P27" t="n">
         <v>60.63</v>
       </c>
-      <c r="O27" t="inlineStr">
+      <c r="Q27" t="inlineStr">
         <is>
           <t>Boxing &amp; MMA</t>
         </is>
@@ -2768,39 +2898,45 @@
         </is>
       </c>
       <c r="D28" t="n">
+        <v>90</v>
+      </c>
+      <c r="E28" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="F28" t="n">
         <v>44585.09</v>
       </c>
-      <c r="E28" t="n">
+      <c r="G28" t="n">
         <v>991</v>
       </c>
-      <c r="F28" t="n">
+      <c r="H28" t="n">
         <v>327</v>
       </c>
-      <c r="G28" t="n">
+      <c r="I28" t="n">
         <v>44.99</v>
       </c>
-      <c r="H28" t="n">
+      <c r="J28" t="n">
         <v>6.12</v>
       </c>
-      <c r="I28" t="n">
+      <c r="K28" t="n">
         <v>6.13</v>
       </c>
-      <c r="J28" t="n">
+      <c r="L28" t="n">
         <v>0.66</v>
       </c>
-      <c r="K28" t="n">
+      <c r="M28" t="n">
         <v>0.51</v>
       </c>
-      <c r="L28" t="n">
-        <v>7.19</v>
-      </c>
-      <c r="M28" t="n">
-        <v>10.28</v>
-      </c>
       <c r="N28" t="n">
+        <v>5.59</v>
+      </c>
+      <c r="O28" t="n">
+        <v>8.68</v>
+      </c>
+      <c r="P28" t="n">
         <v>57.93</v>
       </c>
-      <c r="O28" t="inlineStr">
+      <c r="Q28" t="inlineStr">
         <is>
           <t>Tennis &amp; Racquet</t>
         </is>
@@ -2823,39 +2959,45 @@
         </is>
       </c>
       <c r="D29" t="n">
+        <v>90</v>
+      </c>
+      <c r="E29" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="F29" t="n">
         <v>44243.49</v>
       </c>
-      <c r="E29" t="n">
+      <c r="G29" t="n">
         <v>851</v>
       </c>
-      <c r="F29" t="n">
+      <c r="H29" t="n">
         <v>291</v>
       </c>
-      <c r="G29" t="n">
+      <c r="I29" t="n">
         <v>51.99</v>
       </c>
-      <c r="H29" t="n">
+      <c r="J29" t="n">
         <v>5.25</v>
       </c>
-      <c r="I29" t="n">
+      <c r="K29" t="n">
         <v>4.77</v>
       </c>
-      <c r="J29" t="n">
+      <c r="L29" t="n">
         <v>0.6899999999999999</v>
       </c>
-      <c r="K29" t="n">
+      <c r="M29" t="n">
         <v>0.5</v>
       </c>
-      <c r="L29" t="n">
-        <v>5.57</v>
-      </c>
-      <c r="M29" t="n">
-        <v>8.199999999999999</v>
-      </c>
       <c r="N29" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="O29" t="n">
+        <v>6.96</v>
+      </c>
+      <c r="P29" t="n">
         <v>63.01</v>
       </c>
-      <c r="O29" t="inlineStr">
+      <c r="Q29" t="inlineStr">
         <is>
           <t>Electronics</t>
         </is>
@@ -2878,39 +3020,45 @@
         </is>
       </c>
       <c r="D30" t="n">
+        <v>90</v>
+      </c>
+      <c r="E30" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="F30" t="n">
         <v>43856.8</v>
       </c>
-      <c r="E30" t="n">
+      <c r="G30" t="n">
         <v>208</v>
       </c>
-      <c r="F30" t="n">
+      <c r="H30" t="n">
         <v>208</v>
       </c>
-      <c r="G30" t="n">
+      <c r="I30" t="n">
         <v>210.85</v>
       </c>
-      <c r="H30" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="I30" t="n">
+      <c r="J30" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="K30" t="n">
         <v>14.1</v>
       </c>
-      <c r="J30" t="n">
+      <c r="L30" t="n">
         <v>5.23</v>
       </c>
-      <c r="K30" t="n">
+      <c r="M30" t="n">
         <v>0.49</v>
       </c>
-      <c r="L30" t="n">
-        <v>16.26</v>
-      </c>
-      <c r="M30" t="n">
-        <v>16.89</v>
-      </c>
       <c r="N30" t="n">
+        <v>12.64</v>
+      </c>
+      <c r="O30" t="n">
+        <v>13.27</v>
+      </c>
+      <c r="P30" t="n">
         <v>56.73</v>
       </c>
-      <c r="O30" t="inlineStr">
+      <c r="Q30" t="inlineStr">
         <is>
           <t>Men's Clothing</t>
         </is>
@@ -2933,39 +3081,45 @@
         </is>
       </c>
       <c r="D31" t="n">
+        <v>90</v>
+      </c>
+      <c r="E31" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="F31" t="n">
         <v>41524.8</v>
       </c>
-      <c r="E31" t="n">
+      <c r="G31" t="n">
         <v>492</v>
       </c>
-      <c r="F31" t="n">
+      <c r="H31" t="n">
         <v>492</v>
       </c>
-      <c r="G31" t="n">
+      <c r="I31" t="n">
         <v>84.40000000000001</v>
       </c>
-      <c r="H31" t="n">
+      <c r="J31" t="n">
         <v>3.04</v>
       </c>
-      <c r="I31" t="n">
+      <c r="K31" t="n">
         <v>24.08</v>
       </c>
-      <c r="J31" t="n">
+      <c r="L31" t="n">
         <v>3.64</v>
       </c>
-      <c r="K31" t="n">
+      <c r="M31" t="n">
         <v>0.48</v>
       </c>
-      <c r="L31" t="n">
-        <v>27.65</v>
-      </c>
-      <c r="M31" t="n">
-        <v>29.12</v>
-      </c>
       <c r="N31" t="n">
+        <v>21.48</v>
+      </c>
+      <c r="O31" t="n">
+        <v>22.95</v>
+      </c>
+      <c r="P31" t="n">
         <v>61.38</v>
       </c>
-      <c r="O31" t="inlineStr">
+      <c r="Q31" t="inlineStr">
         <is>
           <t>Pet Supplies</t>
         </is>
@@ -2988,39 +3142,45 @@
         </is>
       </c>
       <c r="D32" t="n">
+        <v>90</v>
+      </c>
+      <c r="E32" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="F32" t="n">
         <v>41415.37</v>
       </c>
-      <c r="E32" t="n">
+      <c r="G32" t="n">
         <v>863</v>
       </c>
-      <c r="F32" t="n">
+      <c r="H32" t="n">
         <v>291</v>
       </c>
-      <c r="G32" t="n">
+      <c r="I32" t="n">
         <v>47.99</v>
       </c>
-      <c r="H32" t="n">
+      <c r="J32" t="n">
         <v>5.33</v>
       </c>
-      <c r="I32" t="n">
+      <c r="K32" t="n">
         <v>5.56</v>
       </c>
-      <c r="J32" t="n">
+      <c r="L32" t="n">
         <v>0.67</v>
       </c>
-      <c r="K32" t="n">
+      <c r="M32" t="n">
         <v>0.49</v>
       </c>
-      <c r="L32" t="n">
-        <v>6.41</v>
-      </c>
-      <c r="M32" t="n">
-        <v>9.01</v>
-      </c>
       <c r="N32" t="n">
+        <v>4.98</v>
+      </c>
+      <c r="O32" t="n">
+        <v>7.58</v>
+      </c>
+      <c r="P32" t="n">
         <v>52.92</v>
       </c>
-      <c r="O32" t="inlineStr">
+      <c r="Q32" t="inlineStr">
         <is>
           <t>Electronics</t>
         </is>
@@ -3043,39 +3203,45 @@
         </is>
       </c>
       <c r="D33" t="n">
+        <v>90</v>
+      </c>
+      <c r="E33" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="F33" t="n">
         <v>38392</v>
       </c>
-      <c r="E33" t="n">
+      <c r="G33" t="n">
         <v>800</v>
       </c>
-      <c r="F33" t="n">
+      <c r="H33" t="n">
         <v>264</v>
       </c>
-      <c r="G33" t="n">
+      <c r="I33" t="n">
         <v>47.99</v>
       </c>
-      <c r="H33" t="n">
+      <c r="J33" t="n">
         <v>4.94</v>
       </c>
-      <c r="I33" t="n">
+      <c r="K33" t="n">
         <v>5.18</v>
       </c>
-      <c r="J33" t="n">
+      <c r="L33" t="n">
         <v>0.67</v>
       </c>
-      <c r="K33" t="n">
+      <c r="M33" t="n">
         <v>0.52</v>
       </c>
-      <c r="L33" t="n">
-        <v>6.18</v>
-      </c>
-      <c r="M33" t="n">
-        <v>8.76</v>
-      </c>
       <c r="N33" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="O33" t="n">
+        <v>7.38</v>
+      </c>
+      <c r="P33" t="n">
         <v>57.74</v>
       </c>
-      <c r="O33" t="inlineStr">
+      <c r="Q33" t="inlineStr">
         <is>
           <t>Electronics</t>
         </is>
@@ -3098,39 +3264,45 @@
         </is>
       </c>
       <c r="D34" t="n">
+        <v>90</v>
+      </c>
+      <c r="E34" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="F34" t="n">
         <v>36576.87</v>
       </c>
-      <c r="E34" t="n">
+      <c r="G34" t="n">
         <v>813</v>
       </c>
-      <c r="F34" t="n">
+      <c r="H34" t="n">
         <v>279</v>
       </c>
-      <c r="G34" t="n">
+      <c r="I34" t="n">
         <v>44.99</v>
       </c>
-      <c r="H34" t="n">
+      <c r="J34" t="n">
         <v>5.02</v>
       </c>
-      <c r="I34" t="n">
+      <c r="K34" t="n">
         <v>5.1</v>
       </c>
-      <c r="J34" t="n">
+      <c r="L34" t="n">
         <v>0.6899999999999999</v>
       </c>
-      <c r="K34" t="n">
+      <c r="M34" t="n">
         <v>0.47</v>
       </c>
-      <c r="L34" t="n">
-        <v>5.76</v>
-      </c>
-      <c r="M34" t="n">
-        <v>8.109999999999999</v>
-      </c>
       <c r="N34" t="n">
+        <v>4.48</v>
+      </c>
+      <c r="O34" t="n">
+        <v>6.83</v>
+      </c>
+      <c r="P34" t="n">
         <v>55</v>
       </c>
-      <c r="O34" t="inlineStr">
+      <c r="Q34" t="inlineStr">
         <is>
           <t>Electronics</t>
         </is>
@@ -3153,39 +3325,45 @@
         </is>
       </c>
       <c r="D35" t="n">
+        <v>90</v>
+      </c>
+      <c r="E35" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="F35" t="n">
         <v>35191.2</v>
       </c>
-      <c r="E35" t="n">
+      <c r="G35" t="n">
         <v>880</v>
       </c>
-      <c r="F35" t="n">
+      <c r="H35" t="n">
         <v>298</v>
       </c>
-      <c r="G35" t="n">
+      <c r="I35" t="n">
         <v>39.99</v>
       </c>
-      <c r="H35" t="n">
+      <c r="J35" t="n">
         <v>5.43</v>
       </c>
-      <c r="I35" t="n">
+      <c r="K35" t="n">
         <v>5.4</v>
       </c>
-      <c r="J35" t="n">
+      <c r="L35" t="n">
         <v>0.71</v>
       </c>
-      <c r="K35" t="n">
+      <c r="M35" t="n">
         <v>0.49</v>
       </c>
-      <c r="L35" t="n">
-        <v>6.26</v>
-      </c>
-      <c r="M35" t="n">
-        <v>8.94</v>
-      </c>
       <c r="N35" t="n">
+        <v>4.87</v>
+      </c>
+      <c r="O35" t="n">
+        <v>7.55</v>
+      </c>
+      <c r="P35" t="n">
         <v>55.67</v>
       </c>
-      <c r="O35" t="inlineStr">
+      <c r="Q35" t="inlineStr">
         <is>
           <t>Girls' Apparel</t>
         </is>
@@ -3208,39 +3386,45 @@
         </is>
       </c>
       <c r="D36" t="n">
+        <v>90</v>
+      </c>
+      <c r="E36" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="F36" t="n">
         <v>34671.33</v>
       </c>
-      <c r="E36" t="n">
+      <c r="G36" t="n">
         <v>867</v>
       </c>
-      <c r="F36" t="n">
+      <c r="H36" t="n">
         <v>284</v>
       </c>
-      <c r="G36" t="n">
+      <c r="I36" t="n">
         <v>39.99</v>
       </c>
-      <c r="H36" t="n">
+      <c r="J36" t="n">
         <v>5.35</v>
       </c>
-      <c r="I36" t="n">
+      <c r="K36" t="n">
         <v>5.42</v>
       </c>
-      <c r="J36" t="n">
+      <c r="L36" t="n">
         <v>0.71</v>
       </c>
-      <c r="K36" t="n">
+      <c r="M36" t="n">
         <v>0.49</v>
       </c>
-      <c r="L36" t="n">
-        <v>6.27</v>
-      </c>
-      <c r="M36" t="n">
-        <v>8.9</v>
-      </c>
       <c r="N36" t="n">
+        <v>4.87</v>
+      </c>
+      <c r="O36" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="P36" t="n">
         <v>59.86</v>
       </c>
-      <c r="O36" t="inlineStr">
+      <c r="Q36" t="inlineStr">
         <is>
           <t>Golf Gloves</t>
         </is>
@@ -3263,39 +3447,45 @@
         </is>
       </c>
       <c r="D37" t="n">
+        <v>90</v>
+      </c>
+      <c r="E37" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="F37" t="n">
         <v>33310.5</v>
       </c>
-      <c r="E37" t="n">
+      <c r="G37" t="n">
         <v>838</v>
       </c>
-      <c r="F37" t="n">
+      <c r="H37" t="n">
         <v>838</v>
       </c>
-      <c r="G37" t="n">
+      <c r="I37" t="n">
         <v>39.75</v>
       </c>
-      <c r="H37" t="n">
+      <c r="J37" t="n">
         <v>5.17</v>
       </c>
-      <c r="I37" t="n">
+      <c r="K37" t="n">
         <v>36.37</v>
       </c>
-      <c r="J37" t="n">
+      <c r="L37" t="n">
         <v>4.68</v>
       </c>
-      <c r="K37" t="n">
+      <c r="M37" t="n">
         <v>0.51</v>
       </c>
-      <c r="L37" t="n">
-        <v>42.98</v>
-      </c>
-      <c r="M37" t="n">
-        <v>45.63</v>
-      </c>
       <c r="N37" t="n">
+        <v>33.39</v>
+      </c>
+      <c r="O37" t="n">
+        <v>36.04</v>
+      </c>
+      <c r="P37" t="n">
         <v>56.32</v>
       </c>
-      <c r="O37" t="inlineStr">
+      <c r="Q37" t="inlineStr">
         <is>
           <t>Video Games</t>
         </is>
@@ -3318,39 +3508,45 @@
         </is>
       </c>
       <c r="D38" t="n">
+        <v>90</v>
+      </c>
+      <c r="E38" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="F38" t="n">
         <v>29999.85</v>
       </c>
-      <c r="E38" t="n">
+      <c r="G38" t="n">
         <v>15</v>
       </c>
-      <c r="F38" t="n">
+      <c r="H38" t="n">
         <v>15</v>
       </c>
-      <c r="G38" t="n">
+      <c r="I38" t="n">
         <v>1999.99</v>
       </c>
-      <c r="H38" t="n">
+      <c r="J38" t="n">
         <v>0.09</v>
       </c>
-      <c r="I38" t="n">
+      <c r="K38" t="n">
         <v>0.88</v>
       </c>
-      <c r="J38" t="n">
+      <c r="L38" t="n">
         <v>4.33</v>
       </c>
-      <c r="K38" t="n">
+      <c r="M38" t="n">
         <v>0.5</v>
       </c>
-      <c r="L38" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="M38" t="n">
-        <v>1.08</v>
-      </c>
       <c r="N38" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="O38" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="P38" t="n">
         <v>40</v>
       </c>
-      <c r="O38" t="inlineStr">
+      <c r="Q38" t="inlineStr">
         <is>
           <t>Strength Training</t>
         </is>
@@ -3373,39 +3569,45 @@
         </is>
       </c>
       <c r="D39" t="n">
+        <v>90</v>
+      </c>
+      <c r="E39" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="F39" t="n">
         <v>29930.02</v>
       </c>
-      <c r="E39" t="n">
+      <c r="G39" t="n">
         <v>998</v>
       </c>
-      <c r="F39" t="n">
+      <c r="H39" t="n">
         <v>321</v>
       </c>
-      <c r="G39" t="n">
+      <c r="I39" t="n">
         <v>29.99</v>
       </c>
-      <c r="H39" t="n">
+      <c r="J39" t="n">
         <v>6.16</v>
       </c>
-      <c r="I39" t="n">
+      <c r="K39" t="n">
         <v>6.13</v>
       </c>
-      <c r="J39" t="n">
+      <c r="L39" t="n">
         <v>0.67</v>
       </c>
-      <c r="K39" t="n">
+      <c r="M39" t="n">
         <v>0.49</v>
       </c>
-      <c r="L39" t="n">
-        <v>7.11</v>
-      </c>
-      <c r="M39" t="n">
-        <v>10.15</v>
-      </c>
       <c r="N39" t="n">
+        <v>5.53</v>
+      </c>
+      <c r="O39" t="n">
+        <v>8.57</v>
+      </c>
+      <c r="P39" t="n">
         <v>60.37</v>
       </c>
-      <c r="O39" t="inlineStr">
+      <c r="Q39" t="inlineStr">
         <is>
           <t>Hunting &amp; Shooting</t>
         </is>
@@ -3428,39 +3630,45 @@
         </is>
       </c>
       <c r="D40" t="n">
+        <v>90</v>
+      </c>
+      <c r="E40" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="F40" t="n">
         <v>29686.72</v>
       </c>
-      <c r="E40" t="n">
+      <c r="G40" t="n">
         <v>928</v>
       </c>
-      <c r="F40" t="n">
+      <c r="H40" t="n">
         <v>308</v>
       </c>
-      <c r="G40" t="n">
+      <c r="I40" t="n">
         <v>31.99</v>
       </c>
-      <c r="H40" t="n">
+      <c r="J40" t="n">
         <v>5.73</v>
       </c>
-      <c r="I40" t="n">
+      <c r="K40" t="n">
         <v>5.73</v>
       </c>
-      <c r="J40" t="n">
+      <c r="L40" t="n">
         <v>0.71</v>
       </c>
-      <c r="K40" t="n">
+      <c r="M40" t="n">
         <v>0.52</v>
       </c>
-      <c r="L40" t="n">
-        <v>6.79</v>
-      </c>
-      <c r="M40" t="n">
-        <v>9.74</v>
-      </c>
       <c r="N40" t="n">
+        <v>5.28</v>
+      </c>
+      <c r="O40" t="n">
+        <v>8.23</v>
+      </c>
+      <c r="P40" t="n">
         <v>61.36</v>
       </c>
-      <c r="O40" t="inlineStr">
+      <c r="Q40" t="inlineStr">
         <is>
           <t>Electronics</t>
         </is>
@@ -3483,39 +3691,45 @@
         </is>
       </c>
       <c r="D41" t="n">
+        <v>90</v>
+      </c>
+      <c r="E41" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="F41" t="n">
         <v>29601.54</v>
       </c>
-      <c r="E41" t="n">
+      <c r="G41" t="n">
         <v>846</v>
       </c>
-      <c r="F41" t="n">
+      <c r="H41" t="n">
         <v>297</v>
       </c>
-      <c r="G41" t="n">
+      <c r="I41" t="n">
         <v>34.99</v>
       </c>
-      <c r="H41" t="n">
+      <c r="J41" t="n">
         <v>5.22</v>
       </c>
-      <c r="I41" t="n">
+      <c r="K41" t="n">
         <v>5.42</v>
       </c>
-      <c r="J41" t="n">
+      <c r="L41" t="n">
         <v>0.72</v>
       </c>
-      <c r="K41" t="n">
+      <c r="M41" t="n">
         <v>0.51</v>
       </c>
-      <c r="L41" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="M41" t="n">
-        <v>9.07</v>
-      </c>
       <c r="N41" t="n">
+        <v>4.97</v>
+      </c>
+      <c r="O41" t="n">
+        <v>7.64</v>
+      </c>
+      <c r="P41" t="n">
         <v>59.53</v>
       </c>
-      <c r="O41" t="inlineStr">
+      <c r="Q41" t="inlineStr">
         <is>
           <t>Fitness Accessories</t>
         </is>
@@ -3538,39 +3752,45 @@
         </is>
       </c>
       <c r="D42" t="n">
+        <v>90</v>
+      </c>
+      <c r="E42" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="F42" t="n">
         <v>29398.81</v>
       </c>
-      <c r="E42" t="n">
+      <c r="G42" t="n">
         <v>919</v>
       </c>
-      <c r="F42" t="n">
+      <c r="H42" t="n">
         <v>306</v>
       </c>
-      <c r="G42" t="n">
+      <c r="I42" t="n">
         <v>31.99</v>
       </c>
-      <c r="H42" t="n">
+      <c r="J42" t="n">
         <v>5.67</v>
       </c>
-      <c r="I42" t="n">
+      <c r="K42" t="n">
         <v>5.76</v>
       </c>
-      <c r="J42" t="n">
+      <c r="L42" t="n">
         <v>0.77</v>
       </c>
-      <c r="K42" t="n">
+      <c r="M42" t="n">
         <v>0.52</v>
       </c>
-      <c r="L42" t="n">
-        <v>6.86</v>
-      </c>
-      <c r="M42" t="n">
-        <v>9.82</v>
-      </c>
       <c r="N42" t="n">
+        <v>5.33</v>
+      </c>
+      <c r="O42" t="n">
+        <v>8.289999999999999</v>
+      </c>
+      <c r="P42" t="n">
         <v>59.49</v>
       </c>
-      <c r="O42" t="inlineStr">
+      <c r="Q42" t="inlineStr">
         <is>
           <t>Electronics</t>
         </is>
@@ -3593,39 +3813,45 @@
         </is>
       </c>
       <c r="D43" t="n">
+        <v>90</v>
+      </c>
+      <c r="E43" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="F43" t="n">
         <v>28982.94</v>
       </c>
-      <c r="E43" t="n">
+      <c r="G43" t="n">
         <v>906</v>
       </c>
-      <c r="F43" t="n">
+      <c r="H43" t="n">
         <v>309</v>
       </c>
-      <c r="G43" t="n">
+      <c r="I43" t="n">
         <v>31.99</v>
       </c>
-      <c r="H43" t="n">
+      <c r="J43" t="n">
         <v>5.59</v>
       </c>
-      <c r="I43" t="n">
+      <c r="K43" t="n">
         <v>5.56</v>
       </c>
-      <c r="J43" t="n">
+      <c r="L43" t="n">
         <v>0.66</v>
       </c>
-      <c r="K43" t="n">
+      <c r="M43" t="n">
         <v>0.5</v>
       </c>
-      <c r="L43" t="n">
-        <v>6.49</v>
-      </c>
-      <c r="M43" t="n">
-        <v>9.279999999999999</v>
-      </c>
       <c r="N43" t="n">
+        <v>5.04</v>
+      </c>
+      <c r="O43" t="n">
+        <v>7.84</v>
+      </c>
+      <c r="P43" t="n">
         <v>57.74</v>
       </c>
-      <c r="O43" t="inlineStr">
+      <c r="Q43" t="inlineStr">
         <is>
           <t>Electronics</t>
         </is>
@@ -3648,39 +3874,45 @@
         </is>
       </c>
       <c r="D44" t="n">
+        <v>90</v>
+      </c>
+      <c r="E44" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="F44" t="n">
         <v>27840</v>
       </c>
-      <c r="E44" t="n">
+      <c r="G44" t="n">
         <v>928</v>
       </c>
-      <c r="F44" t="n">
+      <c r="H44" t="n">
         <v>304</v>
       </c>
-      <c r="G44" t="n">
+      <c r="I44" t="n">
         <v>30</v>
       </c>
-      <c r="H44" t="n">
+      <c r="J44" t="n">
         <v>5.73</v>
       </c>
-      <c r="I44" t="n">
+      <c r="K44" t="n">
         <v>5.76</v>
       </c>
-      <c r="J44" t="n">
+      <c r="L44" t="n">
         <v>0.7</v>
       </c>
-      <c r="K44" t="n">
+      <c r="M44" t="n">
         <v>0.5</v>
       </c>
-      <c r="L44" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="M44" t="n">
-        <v>9.550000000000001</v>
-      </c>
       <c r="N44" t="n">
+        <v>5.21</v>
+      </c>
+      <c r="O44" t="n">
+        <v>8.06</v>
+      </c>
+      <c r="P44" t="n">
         <v>55.26</v>
       </c>
-      <c r="O44" t="inlineStr">
+      <c r="Q44" t="inlineStr">
         <is>
           <t>Shop By Sport</t>
         </is>
@@ -3703,39 +3935,45 @@
         </is>
       </c>
       <c r="D45" t="n">
+        <v>90</v>
+      </c>
+      <c r="E45" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="F45" t="n">
         <v>27327.19</v>
       </c>
-      <c r="E45" t="n">
+      <c r="G45" t="n">
         <v>781</v>
       </c>
-      <c r="F45" t="n">
+      <c r="H45" t="n">
         <v>262</v>
       </c>
-      <c r="G45" t="n">
+      <c r="I45" t="n">
         <v>34.99</v>
       </c>
-      <c r="H45" t="n">
+      <c r="J45" t="n">
         <v>4.82</v>
       </c>
-      <c r="I45" t="n">
+      <c r="K45" t="n">
         <v>4.86</v>
       </c>
-      <c r="J45" t="n">
+      <c r="L45" t="n">
         <v>0.75</v>
       </c>
-      <c r="K45" t="n">
+      <c r="M45" t="n">
         <v>0.49</v>
       </c>
-      <c r="L45" t="n">
-        <v>5.64</v>
-      </c>
-      <c r="M45" t="n">
-        <v>8.02</v>
-      </c>
       <c r="N45" t="n">
+        <v>4.38</v>
+      </c>
+      <c r="O45" t="n">
+        <v>6.76</v>
+      </c>
+      <c r="P45" t="n">
         <v>61.45</v>
       </c>
-      <c r="O45" t="inlineStr">
+      <c r="Q45" t="inlineStr">
         <is>
           <t>Baseball &amp; Softball</t>
         </is>
@@ -3758,39 +3996,45 @@
         </is>
       </c>
       <c r="D46" t="n">
+        <v>90</v>
+      </c>
+      <c r="E46" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="F46" t="n">
         <v>27210</v>
       </c>
-      <c r="E46" t="n">
+      <c r="G46" t="n">
         <v>907</v>
       </c>
-      <c r="F46" t="n">
+      <c r="H46" t="n">
         <v>318</v>
       </c>
-      <c r="G46" t="n">
+      <c r="I46" t="n">
         <v>30</v>
       </c>
-      <c r="H46" t="n">
+      <c r="J46" t="n">
         <v>5.6</v>
       </c>
-      <c r="I46" t="n">
+      <c r="K46" t="n">
         <v>5.87</v>
       </c>
-      <c r="J46" t="n">
+      <c r="L46" t="n">
         <v>0.72</v>
       </c>
-      <c r="K46" t="n">
+      <c r="M46" t="n">
         <v>0.51</v>
       </c>
-      <c r="L46" t="n">
-        <v>6.89</v>
-      </c>
-      <c r="M46" t="n">
-        <v>9.720000000000001</v>
-      </c>
       <c r="N46" t="n">
+        <v>5.35</v>
+      </c>
+      <c r="O46" t="n">
+        <v>8.18</v>
+      </c>
+      <c r="P46" t="n">
         <v>58.18</v>
       </c>
-      <c r="O46" t="inlineStr">
+      <c r="Q46" t="inlineStr">
         <is>
           <t>Cardio Equipment</t>
         </is>
@@ -3813,39 +4057,45 @@
         </is>
       </c>
       <c r="D47" t="n">
+        <v>90</v>
+      </c>
+      <c r="E47" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="F47" t="n">
         <v>27210</v>
       </c>
-      <c r="E47" t="n">
+      <c r="G47" t="n">
         <v>907</v>
       </c>
-      <c r="F47" t="n">
+      <c r="H47" t="n">
         <v>297</v>
       </c>
-      <c r="G47" t="n">
+      <c r="I47" t="n">
         <v>30</v>
       </c>
-      <c r="H47" t="n">
+      <c r="J47" t="n">
         <v>5.6</v>
       </c>
-      <c r="I47" t="n">
+      <c r="K47" t="n">
         <v>5.97</v>
       </c>
-      <c r="J47" t="n">
+      <c r="L47" t="n">
         <v>0.72</v>
       </c>
-      <c r="K47" t="n">
+      <c r="M47" t="n">
         <v>0.49</v>
       </c>
-      <c r="L47" t="n">
-        <v>6.92</v>
-      </c>
-      <c r="M47" t="n">
-        <v>9.68</v>
-      </c>
       <c r="N47" t="n">
+        <v>5.37</v>
+      </c>
+      <c r="O47" t="n">
+        <v>8.130000000000001</v>
+      </c>
+      <c r="P47" t="n">
         <v>60.4</v>
       </c>
-      <c r="O47" t="inlineStr">
+      <c r="Q47" t="inlineStr">
         <is>
           <t>Girls' Apparel</t>
         </is>
@@ -3868,39 +4118,45 @@
         </is>
       </c>
       <c r="D48" t="n">
+        <v>90</v>
+      </c>
+      <c r="E48" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="F48" t="n">
         <v>27127.52</v>
       </c>
-      <c r="E48" t="n">
+      <c r="G48" t="n">
         <v>848</v>
       </c>
-      <c r="F48" t="n">
+      <c r="H48" t="n">
         <v>285</v>
       </c>
-      <c r="G48" t="n">
+      <c r="I48" t="n">
         <v>31.99</v>
       </c>
-      <c r="H48" t="n">
+      <c r="J48" t="n">
         <v>5.23</v>
       </c>
-      <c r="I48" t="n">
+      <c r="K48" t="n">
         <v>5.24</v>
       </c>
-      <c r="J48" t="n">
+      <c r="L48" t="n">
         <v>0.7</v>
       </c>
-      <c r="K48" t="n">
+      <c r="M48" t="n">
         <v>0.48</v>
       </c>
-      <c r="L48" t="n">
-        <v>5.98</v>
-      </c>
-      <c r="M48" t="n">
-        <v>8.48</v>
-      </c>
       <c r="N48" t="n">
+        <v>4.65</v>
+      </c>
+      <c r="O48" t="n">
+        <v>7.15</v>
+      </c>
+      <c r="P48" t="n">
         <v>63.51</v>
       </c>
-      <c r="O48" t="inlineStr">
+      <c r="Q48" t="inlineStr">
         <is>
           <t>Electronics</t>
         </is>
@@ -3923,39 +4179,45 @@
         </is>
       </c>
       <c r="D49" t="n">
+        <v>90</v>
+      </c>
+      <c r="E49" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="F49" t="n">
         <v>25751.95</v>
       </c>
-      <c r="E49" t="n">
+      <c r="G49" t="n">
         <v>805</v>
       </c>
-      <c r="F49" t="n">
+      <c r="H49" t="n">
         <v>256</v>
       </c>
-      <c r="G49" t="n">
+      <c r="I49" t="n">
         <v>31.99</v>
       </c>
-      <c r="H49" t="n">
+      <c r="J49" t="n">
         <v>4.97</v>
       </c>
-      <c r="I49" t="n">
+      <c r="K49" t="n">
         <v>5.43</v>
       </c>
-      <c r="J49" t="n">
+      <c r="L49" t="n">
         <v>0.72</v>
       </c>
-      <c r="K49" t="n">
+      <c r="M49" t="n">
         <v>0.52</v>
       </c>
-      <c r="L49" t="n">
-        <v>6.48</v>
-      </c>
-      <c r="M49" t="n">
-        <v>9.08</v>
-      </c>
       <c r="N49" t="n">
+        <v>5.03</v>
+      </c>
+      <c r="O49" t="n">
+        <v>7.63</v>
+      </c>
+      <c r="P49" t="n">
         <v>58.75</v>
       </c>
-      <c r="O49" t="inlineStr">
+      <c r="Q49" t="inlineStr">
         <is>
           <t>Electronics</t>
         </is>
@@ -3978,39 +4240,45 @@
         </is>
       </c>
       <c r="D50" t="n">
+        <v>90</v>
+      </c>
+      <c r="E50" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="F50" t="n">
         <v>23940.42</v>
       </c>
-      <c r="E50" t="n">
+      <c r="G50" t="n">
         <v>958</v>
       </c>
-      <c r="F50" t="n">
+      <c r="H50" t="n">
         <v>313</v>
       </c>
-      <c r="G50" t="n">
+      <c r="I50" t="n">
         <v>24.99</v>
       </c>
-      <c r="H50" t="n">
+      <c r="J50" t="n">
         <v>5.91</v>
       </c>
-      <c r="I50" t="n">
+      <c r="K50" t="n">
         <v>6.01</v>
       </c>
-      <c r="J50" t="n">
+      <c r="L50" t="n">
         <v>0.6899999999999999</v>
       </c>
-      <c r="K50" t="n">
+      <c r="M50" t="n">
         <v>0.51</v>
       </c>
-      <c r="L50" t="n">
-        <v>7.09</v>
-      </c>
-      <c r="M50" t="n">
-        <v>10.11</v>
-      </c>
       <c r="N50" t="n">
+        <v>5.51</v>
+      </c>
+      <c r="O50" t="n">
+        <v>8.529999999999999</v>
+      </c>
+      <c r="P50" t="n">
         <v>65.18000000000001</v>
       </c>
-      <c r="O50" t="inlineStr">
+      <c r="Q50" t="inlineStr">
         <is>
           <t>Accessories</t>
         </is>
@@ -4033,39 +4301,45 @@
         </is>
       </c>
       <c r="D51" t="n">
+        <v>90</v>
+      </c>
+      <c r="E51" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="F51" t="n">
         <v>22865.85</v>
       </c>
-      <c r="E51" t="n">
+      <c r="G51" t="n">
         <v>915</v>
       </c>
-      <c r="F51" t="n">
+      <c r="H51" t="n">
         <v>300</v>
       </c>
-      <c r="G51" t="n">
+      <c r="I51" t="n">
         <v>24.99</v>
       </c>
-      <c r="H51" t="n">
+      <c r="J51" t="n">
         <v>5.65</v>
       </c>
-      <c r="I51" t="n">
+      <c r="K51" t="n">
         <v>5.26</v>
       </c>
-      <c r="J51" t="n">
+      <c r="L51" t="n">
         <v>0.68</v>
       </c>
-      <c r="K51" t="n">
+      <c r="M51" t="n">
         <v>0.5</v>
       </c>
-      <c r="L51" t="n">
-        <v>6.14</v>
-      </c>
-      <c r="M51" t="n">
-        <v>8.960000000000001</v>
-      </c>
       <c r="N51" t="n">
+        <v>4.77</v>
+      </c>
+      <c r="O51" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="P51" t="n">
         <v>58.33</v>
       </c>
-      <c r="O51" t="inlineStr">
+      <c r="Q51" t="inlineStr">
         <is>
           <t>Accessories</t>
         </is>
@@ -4088,39 +4362,45 @@
         </is>
       </c>
       <c r="D52" t="n">
+        <v>90</v>
+      </c>
+      <c r="E52" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="F52" t="n">
         <v>22700</v>
       </c>
-      <c r="E52" t="n">
+      <c r="G52" t="n">
         <v>227</v>
       </c>
-      <c r="F52" t="n">
+      <c r="H52" t="n">
         <v>73</v>
       </c>
-      <c r="G52" t="n">
+      <c r="I52" t="n">
         <v>100</v>
       </c>
-      <c r="H52" t="n">
+      <c r="J52" t="n">
         <v>1.4</v>
       </c>
-      <c r="I52" t="n">
+      <c r="K52" t="n">
         <v>4.49</v>
       </c>
-      <c r="J52" t="n">
+      <c r="L52" t="n">
         <v>2.64</v>
       </c>
-      <c r="K52" t="n">
+      <c r="M52" t="n">
         <v>0.53</v>
       </c>
-      <c r="L52" t="n">
-        <v>5.37</v>
-      </c>
-      <c r="M52" t="n">
-        <v>6.11</v>
-      </c>
       <c r="N52" t="n">
+        <v>4.17</v>
+      </c>
+      <c r="O52" t="n">
+        <v>4.91</v>
+      </c>
+      <c r="P52" t="n">
         <v>57.53</v>
       </c>
-      <c r="O52" t="inlineStr">
+      <c r="Q52" t="inlineStr">
         <is>
           <t>Golf Shoes</t>
         </is>
@@ -4143,39 +4423,45 @@
         </is>
       </c>
       <c r="D53" t="n">
+        <v>90</v>
+      </c>
+      <c r="E53" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="F53" t="n">
         <v>22366.05</v>
       </c>
-      <c r="E53" t="n">
+      <c r="G53" t="n">
         <v>895</v>
       </c>
-      <c r="F53" t="n">
+      <c r="H53" t="n">
         <v>298</v>
       </c>
-      <c r="G53" t="n">
+      <c r="I53" t="n">
         <v>24.99</v>
       </c>
-      <c r="H53" t="n">
+      <c r="J53" t="n">
         <v>5.52</v>
       </c>
-      <c r="I53" t="n">
+      <c r="K53" t="n">
         <v>5.12</v>
       </c>
-      <c r="J53" t="n">
+      <c r="L53" t="n">
         <v>0.66</v>
       </c>
-      <c r="K53" t="n">
+      <c r="M53" t="n">
         <v>0.49</v>
       </c>
-      <c r="L53" t="n">
-        <v>5.93</v>
-      </c>
-      <c r="M53" t="n">
-        <v>8.65</v>
-      </c>
       <c r="N53" t="n">
+        <v>4.61</v>
+      </c>
+      <c r="O53" t="n">
+        <v>7.33</v>
+      </c>
+      <c r="P53" t="n">
         <v>59.2</v>
       </c>
-      <c r="O53" t="inlineStr">
+      <c r="Q53" t="inlineStr">
         <is>
           <t>Accessories</t>
         </is>
@@ -4198,39 +4484,45 @@
         </is>
       </c>
       <c r="D54" t="n">
+        <v>90</v>
+      </c>
+      <c r="E54" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="F54" t="n">
         <v>22252.05</v>
       </c>
-      <c r="E54" t="n">
+      <c r="G54" t="n">
         <v>795</v>
       </c>
-      <c r="F54" t="n">
+      <c r="H54" t="n">
         <v>251</v>
       </c>
-      <c r="G54" t="n">
+      <c r="I54" t="n">
         <v>27.99</v>
       </c>
-      <c r="H54" t="n">
+      <c r="J54" t="n">
         <v>4.91</v>
       </c>
-      <c r="I54" t="n">
+      <c r="K54" t="n">
         <v>4.9</v>
       </c>
-      <c r="J54" t="n">
+      <c r="L54" t="n">
         <v>0.7</v>
       </c>
-      <c r="K54" t="n">
+      <c r="M54" t="n">
         <v>0.48</v>
       </c>
-      <c r="L54" t="n">
-        <v>5.59</v>
-      </c>
-      <c r="M54" t="n">
-        <v>7.94</v>
-      </c>
       <c r="N54" t="n">
+        <v>4.35</v>
+      </c>
+      <c r="O54" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="P54" t="n">
         <v>56.18</v>
       </c>
-      <c r="O54" t="inlineStr">
+      <c r="Q54" t="inlineStr">
         <is>
           <t>Electronics</t>
         </is>
@@ -4253,39 +4545,45 @@
         </is>
       </c>
       <c r="D55" t="n">
+        <v>90</v>
+      </c>
+      <c r="E55" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="F55" t="n">
         <v>22166.13</v>
       </c>
-      <c r="E55" t="n">
+      <c r="G55" t="n">
         <v>887</v>
       </c>
-      <c r="F55" t="n">
+      <c r="H55" t="n">
         <v>293</v>
       </c>
-      <c r="G55" t="n">
+      <c r="I55" t="n">
         <v>24.99</v>
       </c>
-      <c r="H55" t="n">
+      <c r="J55" t="n">
         <v>5.48</v>
       </c>
-      <c r="I55" t="n">
+      <c r="K55" t="n">
         <v>5.49</v>
       </c>
-      <c r="J55" t="n">
+      <c r="L55" t="n">
         <v>0.6899999999999999</v>
       </c>
-      <c r="K55" t="n">
+      <c r="M55" t="n">
         <v>0.5</v>
       </c>
-      <c r="L55" t="n">
-        <v>6.39</v>
-      </c>
-      <c r="M55" t="n">
-        <v>9.109999999999999</v>
-      </c>
       <c r="N55" t="n">
+        <v>4.96</v>
+      </c>
+      <c r="O55" t="n">
+        <v>7.68</v>
+      </c>
+      <c r="P55" t="n">
         <v>56.27</v>
       </c>
-      <c r="O55" t="inlineStr">
+      <c r="Q55" t="inlineStr">
         <is>
           <t>Accessories</t>
         </is>
@@ -4308,39 +4606,45 @@
         </is>
       </c>
       <c r="D56" t="n">
+        <v>90</v>
+      </c>
+      <c r="E56" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="F56" t="n">
         <v>21766.29</v>
       </c>
-      <c r="E56" t="n">
+      <c r="G56" t="n">
         <v>871</v>
       </c>
-      <c r="F56" t="n">
+      <c r="H56" t="n">
         <v>292</v>
       </c>
-      <c r="G56" t="n">
+      <c r="I56" t="n">
         <v>24.99</v>
       </c>
-      <c r="H56" t="n">
+      <c r="J56" t="n">
         <v>5.38</v>
       </c>
-      <c r="I56" t="n">
+      <c r="K56" t="n">
         <v>5.31</v>
       </c>
-      <c r="J56" t="n">
+      <c r="L56" t="n">
         <v>0.7</v>
       </c>
-      <c r="K56" t="n">
+      <c r="M56" t="n">
         <v>0.5</v>
       </c>
-      <c r="L56" t="n">
-        <v>6.18</v>
-      </c>
-      <c r="M56" t="n">
-        <v>8.85</v>
-      </c>
       <c r="N56" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="O56" t="n">
+        <v>7.47</v>
+      </c>
+      <c r="P56" t="n">
         <v>58.56</v>
       </c>
-      <c r="O56" t="inlineStr">
+      <c r="Q56" t="inlineStr">
         <is>
           <t>Accessories</t>
         </is>
@@ -4363,39 +4667,45 @@
         </is>
       </c>
       <c r="D57" t="n">
+        <v>90</v>
+      </c>
+      <c r="E57" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="F57" t="n">
         <v>21475</v>
       </c>
-      <c r="E57" t="n">
+      <c r="G57" t="n">
         <v>859</v>
       </c>
-      <c r="F57" t="n">
+      <c r="H57" t="n">
         <v>289</v>
       </c>
-      <c r="G57" t="n">
+      <c r="I57" t="n">
         <v>25</v>
       </c>
-      <c r="H57" t="n">
+      <c r="J57" t="n">
         <v>5.3</v>
       </c>
-      <c r="I57" t="n">
+      <c r="K57" t="n">
         <v>5.54</v>
       </c>
-      <c r="J57" t="n">
+      <c r="L57" t="n">
         <v>0.6899999999999999</v>
       </c>
-      <c r="K57" t="n">
+      <c r="M57" t="n">
         <v>0.53</v>
       </c>
-      <c r="L57" t="n">
-        <v>6.64</v>
-      </c>
-      <c r="M57" t="n">
-        <v>9.43</v>
-      </c>
       <c r="N57" t="n">
+        <v>5.16</v>
+      </c>
+      <c r="O57" t="n">
+        <v>7.95</v>
+      </c>
+      <c r="P57" t="n">
         <v>63.67</v>
       </c>
-      <c r="O57" t="inlineStr">
+      <c r="Q57" t="inlineStr">
         <is>
           <t>Girls' Apparel</t>
         </is>
@@ -4418,39 +4728,45 @@
         </is>
       </c>
       <c r="D58" t="n">
+        <v>90</v>
+      </c>
+      <c r="E58" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="F58" t="n">
         <v>21116.55</v>
       </c>
-      <c r="E58" t="n">
+      <c r="G58" t="n">
         <v>845</v>
       </c>
-      <c r="F58" t="n">
+      <c r="H58" t="n">
         <v>278</v>
       </c>
-      <c r="G58" t="n">
+      <c r="I58" t="n">
         <v>24.99</v>
       </c>
-      <c r="H58" t="n">
+      <c r="J58" t="n">
         <v>5.22</v>
       </c>
-      <c r="I58" t="n">
+      <c r="K58" t="n">
         <v>5.29</v>
       </c>
-      <c r="J58" t="n">
+      <c r="L58" t="n">
         <v>0.68</v>
       </c>
-      <c r="K58" t="n">
+      <c r="M58" t="n">
         <v>0.51</v>
       </c>
-      <c r="L58" t="n">
-        <v>6.26</v>
-      </c>
-      <c r="M58" t="n">
-        <v>8.94</v>
-      </c>
       <c r="N58" t="n">
+        <v>4.86</v>
+      </c>
+      <c r="O58" t="n">
+        <v>7.54</v>
+      </c>
+      <c r="P58" t="n">
         <v>57.35</v>
       </c>
-      <c r="O58" t="inlineStr">
+      <c r="Q58" t="inlineStr">
         <is>
           <t>Golf Gloves</t>
         </is>
@@ -4473,39 +4789,45 @@
         </is>
       </c>
       <c r="D59" t="n">
+        <v>90</v>
+      </c>
+      <c r="E59" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="F59" t="n">
         <v>20866.65</v>
       </c>
-      <c r="E59" t="n">
+      <c r="G59" t="n">
         <v>835</v>
       </c>
-      <c r="F59" t="n">
+      <c r="H59" t="n">
         <v>279</v>
       </c>
-      <c r="G59" t="n">
+      <c r="I59" t="n">
         <v>24.99</v>
       </c>
-      <c r="H59" t="n">
+      <c r="J59" t="n">
         <v>5.15</v>
       </c>
-      <c r="I59" t="n">
+      <c r="K59" t="n">
         <v>5.49</v>
       </c>
-      <c r="J59" t="n">
+      <c r="L59" t="n">
         <v>0.6899999999999999</v>
       </c>
-      <c r="K59" t="n">
+      <c r="M59" t="n">
         <v>0.52</v>
       </c>
-      <c r="L59" t="n">
-        <v>6.51</v>
-      </c>
-      <c r="M59" t="n">
-        <v>9.17</v>
-      </c>
       <c r="N59" t="n">
+        <v>5.06</v>
+      </c>
+      <c r="O59" t="n">
+        <v>7.72</v>
+      </c>
+      <c r="P59" t="n">
         <v>62.5</v>
       </c>
-      <c r="O59" t="inlineStr">
+      <c r="Q59" t="inlineStr">
         <is>
           <t>Lacrosse</t>
         </is>
@@ -4528,39 +4850,45 @@
         </is>
       </c>
       <c r="D60" t="n">
+        <v>90</v>
+      </c>
+      <c r="E60" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="F60" t="n">
         <v>20697.93</v>
       </c>
-      <c r="E60" t="n">
+      <c r="G60" t="n">
         <v>207</v>
       </c>
-      <c r="F60" t="n">
+      <c r="H60" t="n">
         <v>70</v>
       </c>
-      <c r="G60" t="n">
+      <c r="I60" t="n">
         <v>99.98999999999999</v>
       </c>
-      <c r="H60" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="I60" t="n">
+      <c r="J60" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="K60" t="n">
         <v>3.91</v>
       </c>
-      <c r="J60" t="n">
+      <c r="L60" t="n">
         <v>2.58</v>
       </c>
-      <c r="K60" t="n">
+      <c r="M60" t="n">
         <v>0.54</v>
       </c>
-      <c r="L60" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="M60" t="n">
-        <v>5.44</v>
-      </c>
       <c r="N60" t="n">
+        <v>3.69</v>
+      </c>
+      <c r="O60" t="n">
+        <v>4.38</v>
+      </c>
+      <c r="P60" t="n">
         <v>51.43</v>
       </c>
-      <c r="O60" t="inlineStr">
+      <c r="Q60" t="inlineStr">
         <is>
           <t>Men's Golf Clubs</t>
         </is>
@@ -4583,39 +4911,45 @@
         </is>
       </c>
       <c r="D61" t="n">
+        <v>90</v>
+      </c>
+      <c r="E61" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="F61" t="n">
         <v>20597.94</v>
       </c>
-      <c r="E61" t="n">
+      <c r="G61" t="n">
         <v>206</v>
       </c>
-      <c r="F61" t="n">
+      <c r="H61" t="n">
         <v>68</v>
       </c>
-      <c r="G61" t="n">
+      <c r="I61" t="n">
         <v>99.98999999999999</v>
       </c>
-      <c r="H61" t="n">
+      <c r="J61" t="n">
         <v>1.27</v>
       </c>
-      <c r="I61" t="n">
+      <c r="K61" t="n">
         <v>3.77</v>
       </c>
-      <c r="J61" t="n">
+      <c r="L61" t="n">
         <v>2.7</v>
       </c>
-      <c r="K61" t="n">
+      <c r="M61" t="n">
         <v>0.52</v>
       </c>
-      <c r="L61" t="n">
-        <v>4.48</v>
-      </c>
-      <c r="M61" t="n">
-        <v>5.14</v>
-      </c>
       <c r="N61" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="O61" t="n">
+        <v>4.14</v>
+      </c>
+      <c r="P61" t="n">
         <v>58.82</v>
       </c>
-      <c r="O61" t="inlineStr">
+      <c r="Q61" t="inlineStr">
         <is>
           <t>As Seen on  TV!</t>
         </is>
@@ -4638,39 +4972,45 @@
         </is>
       </c>
       <c r="D62" t="n">
+        <v>90</v>
+      </c>
+      <c r="E62" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="F62" t="n">
         <v>20566.77</v>
       </c>
-      <c r="E62" t="n">
+      <c r="G62" t="n">
         <v>823</v>
       </c>
-      <c r="F62" t="n">
+      <c r="H62" t="n">
         <v>281</v>
       </c>
-      <c r="G62" t="n">
+      <c r="I62" t="n">
         <v>24.99</v>
       </c>
-      <c r="H62" t="n">
+      <c r="J62" t="n">
         <v>5.08</v>
       </c>
-      <c r="I62" t="n">
+      <c r="K62" t="n">
         <v>5.35</v>
       </c>
-      <c r="J62" t="n">
+      <c r="L62" t="n">
         <v>0.76</v>
       </c>
-      <c r="K62" t="n">
+      <c r="M62" t="n">
         <v>0.5</v>
       </c>
-      <c r="L62" t="n">
-        <v>6.24</v>
-      </c>
-      <c r="M62" t="n">
-        <v>8.779999999999999</v>
-      </c>
       <c r="N62" t="n">
+        <v>4.85</v>
+      </c>
+      <c r="O62" t="n">
+        <v>7.39</v>
+      </c>
+      <c r="P62" t="n">
         <v>56.94</v>
       </c>
-      <c r="O62" t="inlineStr">
+      <c r="Q62" t="inlineStr">
         <is>
           <t>Accessories</t>
         </is>
@@ -4693,39 +5033,45 @@
         </is>
       </c>
       <c r="D63" t="n">
+        <v>90</v>
+      </c>
+      <c r="E63" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="F63" t="n">
         <v>20450.7</v>
       </c>
-      <c r="E63" t="n">
+      <c r="G63" t="n">
         <v>930</v>
       </c>
-      <c r="F63" t="n">
+      <c r="H63" t="n">
         <v>294</v>
       </c>
-      <c r="G63" t="n">
+      <c r="I63" t="n">
         <v>21.99</v>
       </c>
-      <c r="H63" t="n">
+      <c r="J63" t="n">
         <v>5.74</v>
       </c>
-      <c r="I63" t="n">
+      <c r="K63" t="n">
         <v>5.57</v>
       </c>
-      <c r="J63" t="n">
+      <c r="L63" t="n">
         <v>0.73</v>
       </c>
-      <c r="K63" t="n">
+      <c r="M63" t="n">
         <v>0.51</v>
       </c>
-      <c r="L63" t="n">
-        <v>6.56</v>
-      </c>
-      <c r="M63" t="n">
-        <v>9.49</v>
-      </c>
       <c r="N63" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="O63" t="n">
+        <v>8.029999999999999</v>
+      </c>
+      <c r="P63" t="n">
         <v>58.98</v>
       </c>
-      <c r="O63" t="inlineStr">
+      <c r="Q63" t="inlineStr">
         <is>
           <t>Trade-In</t>
         </is>
@@ -4748,39 +5094,45 @@
         </is>
       </c>
       <c r="D64" t="n">
+        <v>90</v>
+      </c>
+      <c r="E64" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="F64" t="n">
         <v>20025</v>
       </c>
-      <c r="E64" t="n">
+      <c r="G64" t="n">
         <v>801</v>
       </c>
-      <c r="F64" t="n">
+      <c r="H64" t="n">
         <v>278</v>
       </c>
-      <c r="G64" t="n">
+      <c r="I64" t="n">
         <v>25</v>
       </c>
-      <c r="H64" t="n">
+      <c r="J64" t="n">
         <v>4.94</v>
       </c>
-      <c r="I64" t="n">
+      <c r="K64" t="n">
         <v>5.1</v>
       </c>
-      <c r="J64" t="n">
+      <c r="L64" t="n">
         <v>0.71</v>
       </c>
-      <c r="K64" t="n">
+      <c r="M64" t="n">
         <v>0.49</v>
       </c>
-      <c r="L64" t="n">
-        <v>5.86</v>
-      </c>
-      <c r="M64" t="n">
-        <v>8.26</v>
-      </c>
       <c r="N64" t="n">
+        <v>4.56</v>
+      </c>
+      <c r="O64" t="n">
+        <v>6.96</v>
+      </c>
+      <c r="P64" t="n">
         <v>59.5</v>
       </c>
-      <c r="O64" t="inlineStr">
+      <c r="Q64" t="inlineStr">
         <is>
           <t>Hockey</t>
         </is>
@@ -4803,39 +5155,45 @@
         </is>
       </c>
       <c r="D65" t="n">
+        <v>90</v>
+      </c>
+      <c r="E65" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="F65" t="n">
         <v>19567.94</v>
       </c>
-      <c r="E65" t="n">
+      <c r="G65" t="n">
         <v>206</v>
       </c>
-      <c r="F65" t="n">
+      <c r="H65" t="n">
         <v>70</v>
       </c>
-      <c r="G65" t="n">
+      <c r="I65" t="n">
         <v>94.98999999999999</v>
       </c>
-      <c r="H65" t="n">
+      <c r="J65" t="n">
         <v>1.27</v>
       </c>
-      <c r="I65" t="n">
+      <c r="K65" t="n">
         <v>3.82</v>
       </c>
-      <c r="J65" t="n">
+      <c r="L65" t="n">
         <v>2.54</v>
       </c>
-      <c r="K65" t="n">
+      <c r="M65" t="n">
         <v>0.51</v>
       </c>
-      <c r="L65" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="M65" t="n">
-        <v>5.15</v>
-      </c>
       <c r="N65" t="n">
+        <v>3.49</v>
+      </c>
+      <c r="O65" t="n">
+        <v>4.14</v>
+      </c>
+      <c r="P65" t="n">
         <v>61.43</v>
       </c>
-      <c r="O65" t="inlineStr">
+      <c r="Q65" t="inlineStr">
         <is>
           <t>Boxing &amp; MMA</t>
         </is>
@@ -4858,39 +5216,45 @@
         </is>
       </c>
       <c r="D66" t="n">
+        <v>90</v>
+      </c>
+      <c r="E66" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="F66" t="n">
         <v>19426</v>
       </c>
-      <c r="E66" t="n">
+      <c r="G66" t="n">
         <v>883</v>
       </c>
-      <c r="F66" t="n">
+      <c r="H66" t="n">
         <v>307</v>
       </c>
-      <c r="G66" t="n">
+      <c r="I66" t="n">
         <v>22</v>
       </c>
-      <c r="H66" t="n">
+      <c r="J66" t="n">
         <v>5.45</v>
       </c>
-      <c r="I66" t="n">
+      <c r="K66" t="n">
         <v>5.54</v>
       </c>
-      <c r="J66" t="n">
+      <c r="L66" t="n">
         <v>0.72</v>
       </c>
-      <c r="K66" t="n">
+      <c r="M66" t="n">
         <v>0.49</v>
       </c>
-      <c r="L66" t="n">
-        <v>6.41</v>
-      </c>
-      <c r="M66" t="n">
-        <v>9.09</v>
-      </c>
       <c r="N66" t="n">
+        <v>4.98</v>
+      </c>
+      <c r="O66" t="n">
+        <v>7.66</v>
+      </c>
+      <c r="P66" t="n">
         <v>52.6</v>
       </c>
-      <c r="O66" t="inlineStr">
+      <c r="Q66" t="inlineStr">
         <is>
           <t>Hockey</t>
         </is>
@@ -4913,39 +5277,45 @@
         </is>
       </c>
       <c r="D67" t="n">
+        <v>90</v>
+      </c>
+      <c r="E67" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="F67" t="n">
         <v>19298.07</v>
       </c>
-      <c r="E67" t="n">
+      <c r="G67" t="n">
         <v>193</v>
       </c>
-      <c r="F67" t="n">
+      <c r="H67" t="n">
         <v>63</v>
       </c>
-      <c r="G67" t="n">
+      <c r="I67" t="n">
         <v>99.98999999999999</v>
       </c>
-      <c r="H67" t="n">
+      <c r="J67" t="n">
         <v>1.19</v>
       </c>
-      <c r="I67" t="n">
+      <c r="K67" t="n">
         <v>3.6</v>
       </c>
-      <c r="J67" t="n">
+      <c r="L67" t="n">
         <v>2.66</v>
       </c>
-      <c r="K67" t="n">
+      <c r="M67" t="n">
         <v>0.53</v>
       </c>
-      <c r="L67" t="n">
-        <v>4.34</v>
-      </c>
-      <c r="M67" t="n">
-        <v>4.97</v>
-      </c>
       <c r="N67" t="n">
+        <v>3.37</v>
+      </c>
+      <c r="O67" t="n">
+        <v>4</v>
+      </c>
+      <c r="P67" t="n">
         <v>58.73</v>
       </c>
-      <c r="O67" t="inlineStr">
+      <c r="Q67" t="inlineStr">
         <is>
           <t>Women's Golf Clubs</t>
         </is>
@@ -4968,39 +5338,45 @@
         </is>
       </c>
       <c r="D68" t="n">
+        <v>90</v>
+      </c>
+      <c r="E68" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="F68" t="n">
         <v>19249.23</v>
       </c>
-      <c r="E68" t="n">
+      <c r="G68" t="n">
         <v>77</v>
       </c>
-      <c r="F68" t="n">
+      <c r="H68" t="n">
         <v>75</v>
       </c>
-      <c r="G68" t="n">
+      <c r="I68" t="n">
         <v>249.99</v>
       </c>
-      <c r="H68" t="n">
+      <c r="J68" t="n">
         <v>0.48</v>
       </c>
-      <c r="I68" t="n">
+      <c r="K68" t="n">
         <v>1.47</v>
       </c>
-      <c r="J68" t="n">
+      <c r="L68" t="n">
         <v>2.71</v>
       </c>
-      <c r="K68" t="n">
+      <c r="M68" t="n">
         <v>0.53</v>
       </c>
-      <c r="L68" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="M68" t="n">
-        <v>2.03</v>
-      </c>
       <c r="N68" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="O68" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="P68" t="n">
         <v>63.64</v>
       </c>
-      <c r="O68" t="inlineStr">
+      <c r="Q68" t="inlineStr">
         <is>
           <t>Trade-In</t>
         </is>
@@ -5023,39 +5399,45 @@
         </is>
       </c>
       <c r="D69" t="n">
+        <v>90</v>
+      </c>
+      <c r="E69" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="F69" t="n">
         <v>19077.88</v>
       </c>
-      <c r="E69" t="n">
+      <c r="G69" t="n">
         <v>212</v>
       </c>
-      <c r="F69" t="n">
+      <c r="H69" t="n">
         <v>66</v>
       </c>
-      <c r="G69" t="n">
+      <c r="I69" t="n">
         <v>89.98999999999999</v>
       </c>
-      <c r="H69" t="n">
+      <c r="J69" t="n">
         <v>1.31</v>
       </c>
-      <c r="I69" t="n">
+      <c r="K69" t="n">
         <v>4.08</v>
       </c>
-      <c r="J69" t="n">
+      <c r="L69" t="n">
         <v>2.55</v>
       </c>
-      <c r="K69" t="n">
+      <c r="M69" t="n">
         <v>0.49</v>
       </c>
-      <c r="L69" t="n">
-        <v>4.73</v>
-      </c>
-      <c r="M69" t="n">
-        <v>5.38</v>
-      </c>
       <c r="N69" t="n">
+        <v>3.67</v>
+      </c>
+      <c r="O69" t="n">
+        <v>4.32</v>
+      </c>
+      <c r="P69" t="n">
         <v>51.52</v>
       </c>
-      <c r="O69" t="inlineStr">
+      <c r="Q69" t="inlineStr">
         <is>
           <t>Boxing &amp; MMA</t>
         </is>
@@ -5078,39 +5460,45 @@
         </is>
       </c>
       <c r="D70" t="n">
+        <v>90</v>
+      </c>
+      <c r="E70" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="F70" t="n">
         <v>18810.59</v>
       </c>
-      <c r="E70" t="n">
+      <c r="G70" t="n">
         <v>941</v>
       </c>
-      <c r="F70" t="n">
+      <c r="H70" t="n">
         <v>303</v>
       </c>
-      <c r="G70" t="n">
+      <c r="I70" t="n">
         <v>19.99</v>
       </c>
-      <c r="H70" t="n">
+      <c r="J70" t="n">
         <v>5.81</v>
       </c>
-      <c r="I70" t="n">
+      <c r="K70" t="n">
         <v>6</v>
       </c>
-      <c r="J70" t="n">
+      <c r="L70" t="n">
         <v>0.7</v>
       </c>
-      <c r="K70" t="n">
+      <c r="M70" t="n">
         <v>0.51</v>
       </c>
-      <c r="L70" t="n">
-        <v>7.05</v>
-      </c>
-      <c r="M70" t="n">
-        <v>10</v>
-      </c>
       <c r="N70" t="n">
+        <v>5.48</v>
+      </c>
+      <c r="O70" t="n">
+        <v>8.43</v>
+      </c>
+      <c r="P70" t="n">
         <v>55.05</v>
       </c>
-      <c r="O70" t="inlineStr">
+      <c r="Q70" t="inlineStr">
         <is>
           <t>Golf Balls</t>
         </is>
@@ -5133,39 +5521,45 @@
         </is>
       </c>
       <c r="D71" t="n">
+        <v>90</v>
+      </c>
+      <c r="E71" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="F71" t="n">
         <v>18690.65</v>
       </c>
-      <c r="E71" t="n">
+      <c r="G71" t="n">
         <v>187</v>
       </c>
-      <c r="F71" t="n">
+      <c r="H71" t="n">
         <v>62</v>
       </c>
-      <c r="G71" t="n">
+      <c r="I71" t="n">
         <v>99.95</v>
       </c>
-      <c r="H71" t="n">
+      <c r="J71" t="n">
         <v>1.15</v>
       </c>
-      <c r="I71" t="n">
+      <c r="K71" t="n">
         <v>3.56</v>
       </c>
-      <c r="J71" t="n">
+      <c r="L71" t="n">
         <v>2.55</v>
       </c>
-      <c r="K71" t="n">
+      <c r="M71" t="n">
         <v>0.5</v>
       </c>
-      <c r="L71" t="n">
-        <v>4.17</v>
-      </c>
-      <c r="M71" t="n">
-        <v>4.75</v>
-      </c>
       <c r="N71" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="O71" t="n">
+        <v>3.82</v>
+      </c>
+      <c r="P71" t="n">
         <v>54.84</v>
       </c>
-      <c r="O71" t="inlineStr">
+      <c r="Q71" t="inlineStr">
         <is>
           <t>Kids' Golf Clubs</t>
         </is>
@@ -5188,39 +5582,45 @@
         </is>
       </c>
       <c r="D72" t="n">
+        <v>90</v>
+      </c>
+      <c r="E72" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="F72" t="n">
         <v>18598.14</v>
       </c>
-      <c r="E72" t="n">
+      <c r="G72" t="n">
         <v>186</v>
       </c>
-      <c r="F72" t="n">
+      <c r="H72" t="n">
         <v>62</v>
       </c>
-      <c r="G72" t="n">
+      <c r="I72" t="n">
         <v>99.98999999999999</v>
       </c>
-      <c r="H72" t="n">
+      <c r="J72" t="n">
         <v>1.15</v>
       </c>
-      <c r="I72" t="n">
+      <c r="K72" t="n">
         <v>3.41</v>
       </c>
-      <c r="J72" t="n">
+      <c r="L72" t="n">
         <v>2.55</v>
       </c>
-      <c r="K72" t="n">
+      <c r="M72" t="n">
         <v>0.51</v>
       </c>
-      <c r="L72" t="n">
-        <v>4.04</v>
-      </c>
-      <c r="M72" t="n">
-        <v>4.63</v>
-      </c>
       <c r="N72" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="O72" t="n">
+        <v>3.73</v>
+      </c>
+      <c r="P72" t="n">
         <v>60.32</v>
       </c>
-      <c r="O72" t="inlineStr">
+      <c r="Q72" t="inlineStr">
         <is>
           <t>Lacrosse</t>
         </is>
@@ -5243,39 +5643,45 @@
         </is>
       </c>
       <c r="D73" t="n">
+        <v>90</v>
+      </c>
+      <c r="E73" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="F73" t="n">
         <v>18477.69</v>
       </c>
-      <c r="E73" t="n">
+      <c r="G73" t="n">
         <v>231</v>
       </c>
-      <c r="F73" t="n">
+      <c r="H73" t="n">
         <v>74</v>
       </c>
-      <c r="G73" t="n">
+      <c r="I73" t="n">
         <v>79.98999999999999</v>
       </c>
-      <c r="H73" t="n">
+      <c r="J73" t="n">
         <v>1.43</v>
       </c>
-      <c r="I73" t="n">
+      <c r="K73" t="n">
         <v>4.08</v>
       </c>
-      <c r="J73" t="n">
+      <c r="L73" t="n">
         <v>2.71</v>
       </c>
-      <c r="K73" t="n">
+      <c r="M73" t="n">
         <v>0.51</v>
       </c>
-      <c r="L73" t="n">
-        <v>4.79</v>
-      </c>
-      <c r="M73" t="n">
-        <v>5.52</v>
-      </c>
       <c r="N73" t="n">
+        <v>3.72</v>
+      </c>
+      <c r="O73" t="n">
+        <v>4.45</v>
+      </c>
+      <c r="P73" t="n">
         <v>51.35</v>
       </c>
-      <c r="O73" t="inlineStr">
+      <c r="Q73" t="inlineStr">
         <is>
           <t>Soccer</t>
         </is>
@@ -5298,39 +5704,45 @@
         </is>
       </c>
       <c r="D74" t="n">
+        <v>90</v>
+      </c>
+      <c r="E74" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="F74" t="n">
         <v>17919</v>
       </c>
-      <c r="E74" t="n">
+      <c r="G74" t="n">
         <v>181</v>
       </c>
-      <c r="F74" t="n">
+      <c r="H74" t="n">
         <v>57</v>
       </c>
-      <c r="G74" t="n">
+      <c r="I74" t="n">
         <v>99</v>
       </c>
-      <c r="H74" t="n">
+      <c r="J74" t="n">
         <v>1.12</v>
       </c>
-      <c r="I74" t="n">
+      <c r="K74" t="n">
         <v>3.57</v>
       </c>
-      <c r="J74" t="n">
+      <c r="L74" t="n">
         <v>2.57</v>
       </c>
-      <c r="K74" t="n">
+      <c r="M74" t="n">
         <v>0.49</v>
       </c>
-      <c r="L74" t="n">
-        <v>4.14</v>
-      </c>
-      <c r="M74" t="n">
-        <v>4.69</v>
-      </c>
       <c r="N74" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="O74" t="n">
+        <v>3.77</v>
+      </c>
+      <c r="P74" t="n">
         <v>56.14</v>
       </c>
-      <c r="O74" t="inlineStr">
+      <c r="Q74" t="inlineStr">
         <is>
           <t>Hunting &amp; Shooting</t>
         </is>
@@ -5353,39 +5765,45 @@
         </is>
       </c>
       <c r="D75" t="n">
+        <v>90</v>
+      </c>
+      <c r="E75" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="F75" t="n">
         <v>17731.13</v>
       </c>
-      <c r="E75" t="n">
+      <c r="G75" t="n">
         <v>887</v>
       </c>
-      <c r="F75" t="n">
+      <c r="H75" t="n">
         <v>303</v>
       </c>
-      <c r="G75" t="n">
+      <c r="I75" t="n">
         <v>19.99</v>
       </c>
-      <c r="H75" t="n">
+      <c r="J75" t="n">
         <v>5.48</v>
       </c>
-      <c r="I75" t="n">
+      <c r="K75" t="n">
         <v>5.28</v>
       </c>
-      <c r="J75" t="n">
+      <c r="L75" t="n">
         <v>0.67</v>
       </c>
-      <c r="K75" t="n">
+      <c r="M75" t="n">
         <v>0.51</v>
       </c>
-      <c r="L75" t="n">
-        <v>6.23</v>
-      </c>
-      <c r="M75" t="n">
-        <v>9.029999999999999</v>
-      </c>
       <c r="N75" t="n">
+        <v>4.84</v>
+      </c>
+      <c r="O75" t="n">
+        <v>7.64</v>
+      </c>
+      <c r="P75" t="n">
         <v>55.45</v>
       </c>
-      <c r="O75" t="inlineStr">
+      <c r="Q75" t="inlineStr">
         <is>
           <t>Golf Apparel</t>
         </is>
@@ -5408,39 +5826,45 @@
         </is>
       </c>
       <c r="D76" t="n">
+        <v>90</v>
+      </c>
+      <c r="E76" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="F76" t="n">
         <v>17638.04</v>
       </c>
-      <c r="E76" t="n">
+      <c r="G76" t="n">
         <v>196</v>
       </c>
-      <c r="F76" t="n">
+      <c r="H76" t="n">
         <v>60</v>
       </c>
-      <c r="G76" t="n">
+      <c r="I76" t="n">
         <v>89.98999999999999</v>
       </c>
-      <c r="H76" t="n">
+      <c r="J76" t="n">
         <v>1.21</v>
       </c>
-      <c r="I76" t="n">
+      <c r="K76" t="n">
         <v>3.97</v>
       </c>
-      <c r="J76" t="n">
+      <c r="L76" t="n">
         <v>2.78</v>
       </c>
-      <c r="K76" t="n">
+      <c r="M76" t="n">
         <v>0.5</v>
       </c>
-      <c r="L76" t="n">
-        <v>4.62</v>
-      </c>
-      <c r="M76" t="n">
-        <v>5.22</v>
-      </c>
       <c r="N76" t="n">
+        <v>3.59</v>
+      </c>
+      <c r="O76" t="n">
+        <v>4.19</v>
+      </c>
+      <c r="P76" t="n">
         <v>60</v>
       </c>
-      <c r="O76" t="inlineStr">
+      <c r="Q76" t="inlineStr">
         <is>
           <t>Kids' Golf Clubs</t>
         </is>
@@ -5463,39 +5887,45 @@
         </is>
       </c>
       <c r="D77" t="n">
+        <v>90</v>
+      </c>
+      <c r="E77" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="F77" t="n">
         <v>16637.92</v>
       </c>
-      <c r="E77" t="n">
+      <c r="G77" t="n">
         <v>208</v>
       </c>
-      <c r="F77" t="n">
+      <c r="H77" t="n">
         <v>69</v>
       </c>
-      <c r="G77" t="n">
+      <c r="I77" t="n">
         <v>79.98999999999999</v>
       </c>
-      <c r="H77" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="I77" t="n">
+      <c r="J77" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="K77" t="n">
         <v>4.03</v>
       </c>
-      <c r="J77" t="n">
+      <c r="L77" t="n">
         <v>2.77</v>
       </c>
-      <c r="K77" t="n">
+      <c r="M77" t="n">
         <v>0.48</v>
       </c>
-      <c r="L77" t="n">
-        <v>4.63</v>
-      </c>
-      <c r="M77" t="n">
-        <v>5.25</v>
-      </c>
       <c r="N77" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="O77" t="n">
+        <v>4.22</v>
+      </c>
+      <c r="P77" t="n">
         <v>59.42</v>
       </c>
-      <c r="O77" t="inlineStr">
+      <c r="Q77" t="inlineStr">
         <is>
           <t>Golf Gloves</t>
         </is>
@@ -5518,39 +5948,45 @@
         </is>
       </c>
       <c r="D78" t="n">
+        <v>90</v>
+      </c>
+      <c r="E78" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="F78" t="n">
         <v>16031.98</v>
       </c>
-      <c r="E78" t="n">
+      <c r="G78" t="n">
         <v>802</v>
       </c>
-      <c r="F78" t="n">
+      <c r="H78" t="n">
         <v>275</v>
       </c>
-      <c r="G78" t="n">
+      <c r="I78" t="n">
         <v>19.99</v>
       </c>
-      <c r="H78" t="n">
+      <c r="J78" t="n">
         <v>4.95</v>
       </c>
-      <c r="I78" t="n">
+      <c r="K78" t="n">
         <v>4.64</v>
       </c>
-      <c r="J78" t="n">
+      <c r="L78" t="n">
         <v>0.71</v>
       </c>
-      <c r="K78" t="n">
+      <c r="M78" t="n">
         <v>0.47</v>
       </c>
-      <c r="L78" t="n">
-        <v>5.26</v>
-      </c>
-      <c r="M78" t="n">
-        <v>7.6</v>
-      </c>
       <c r="N78" t="n">
+        <v>4.09</v>
+      </c>
+      <c r="O78" t="n">
+        <v>6.43</v>
+      </c>
+      <c r="P78" t="n">
         <v>56.32</v>
       </c>
-      <c r="O78" t="inlineStr">
+      <c r="Q78" t="inlineStr">
         <is>
           <t>Golf Balls</t>
         </is>
@@ -5573,39 +6009,45 @@
         </is>
       </c>
       <c r="D79" t="n">
+        <v>90</v>
+      </c>
+      <c r="E79" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="F79" t="n">
         <v>15993.11</v>
       </c>
-      <c r="E79" t="n">
+      <c r="G79" t="n">
         <v>889</v>
       </c>
-      <c r="F79" t="n">
+      <c r="H79" t="n">
         <v>295</v>
       </c>
-      <c r="G79" t="n">
+      <c r="I79" t="n">
         <v>17.99</v>
       </c>
-      <c r="H79" t="n">
+      <c r="J79" t="n">
         <v>5.49</v>
       </c>
-      <c r="I79" t="n">
+      <c r="K79" t="n">
         <v>5.43</v>
       </c>
-      <c r="J79" t="n">
+      <c r="L79" t="n">
         <v>0.72</v>
       </c>
-      <c r="K79" t="n">
+      <c r="M79" t="n">
         <v>0.52</v>
       </c>
-      <c r="L79" t="n">
-        <v>6.43</v>
-      </c>
-      <c r="M79" t="n">
-        <v>9.26</v>
-      </c>
       <c r="N79" t="n">
+        <v>5</v>
+      </c>
+      <c r="O79" t="n">
+        <v>7.83</v>
+      </c>
+      <c r="P79" t="n">
         <v>63.76</v>
       </c>
-      <c r="O79" t="inlineStr">
+      <c r="Q79" t="inlineStr">
         <is>
           <t>Golf Balls</t>
         </is>
@@ -5628,39 +6070,45 @@
         </is>
       </c>
       <c r="D80" t="n">
+        <v>90</v>
+      </c>
+      <c r="E80" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="F80" t="n">
         <v>15600</v>
       </c>
-      <c r="E80" t="n">
+      <c r="G80" t="n">
         <v>195</v>
       </c>
-      <c r="F80" t="n">
+      <c r="H80" t="n">
         <v>65</v>
       </c>
-      <c r="G80" t="n">
+      <c r="I80" t="n">
         <v>80</v>
       </c>
-      <c r="H80" t="n">
+      <c r="J80" t="n">
         <v>1.2</v>
       </c>
-      <c r="I80" t="n">
+      <c r="K80" t="n">
         <v>3.55</v>
       </c>
-      <c r="J80" t="n">
+      <c r="L80" t="n">
         <v>2.68</v>
       </c>
-      <c r="K80" t="n">
+      <c r="M80" t="n">
         <v>0.45</v>
       </c>
-      <c r="L80" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="M80" t="n">
-        <v>4.5</v>
-      </c>
       <c r="N80" t="n">
+        <v>3.07</v>
+      </c>
+      <c r="O80" t="n">
+        <v>3.62</v>
+      </c>
+      <c r="P80" t="n">
         <v>50</v>
       </c>
-      <c r="O80" t="inlineStr">
+      <c r="Q80" t="inlineStr">
         <is>
           <t>Golf Shoes</t>
         </is>
@@ -5683,39 +6131,45 @@
         </is>
       </c>
       <c r="D81" t="n">
+        <v>90</v>
+      </c>
+      <c r="E81" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="F81" t="n">
         <v>14870.7</v>
       </c>
-      <c r="E81" t="n">
+      <c r="G81" t="n">
         <v>930</v>
       </c>
-      <c r="F81" t="n">
+      <c r="H81" t="n">
         <v>302</v>
       </c>
-      <c r="G81" t="n">
+      <c r="I81" t="n">
         <v>15.99</v>
       </c>
-      <c r="H81" t="n">
+      <c r="J81" t="n">
         <v>5.74</v>
       </c>
-      <c r="I81" t="n">
+      <c r="K81" t="n">
         <v>5.98</v>
       </c>
-      <c r="J81" t="n">
+      <c r="L81" t="n">
         <v>0.71</v>
       </c>
-      <c r="K81" t="n">
+      <c r="M81" t="n">
         <v>0.5</v>
       </c>
-      <c r="L81" t="n">
-        <v>6.97</v>
-      </c>
-      <c r="M81" t="n">
-        <v>9.83</v>
-      </c>
       <c r="N81" t="n">
+        <v>5.41</v>
+      </c>
+      <c r="O81" t="n">
+        <v>8.27</v>
+      </c>
+      <c r="P81" t="n">
         <v>57.62</v>
       </c>
-      <c r="O81" t="inlineStr">
+      <c r="Q81" t="inlineStr">
         <is>
           <t>Trade-In</t>
         </is>
@@ -5738,39 +6192,45 @@
         </is>
       </c>
       <c r="D82" t="n">
+        <v>90</v>
+      </c>
+      <c r="E82" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="F82" t="n">
         <v>14151.15</v>
       </c>
-      <c r="E82" t="n">
+      <c r="G82" t="n">
         <v>885</v>
       </c>
-      <c r="F82" t="n">
+      <c r="H82" t="n">
         <v>298</v>
       </c>
-      <c r="G82" t="n">
+      <c r="I82" t="n">
         <v>15.99</v>
       </c>
-      <c r="H82" t="n">
+      <c r="J82" t="n">
         <v>5.46</v>
       </c>
-      <c r="I82" t="n">
+      <c r="K82" t="n">
         <v>5.38</v>
       </c>
-      <c r="J82" t="n">
+      <c r="L82" t="n">
         <v>0.72</v>
       </c>
-      <c r="K82" t="n">
+      <c r="M82" t="n">
         <v>0.52</v>
       </c>
-      <c r="L82" t="n">
-        <v>6.37</v>
-      </c>
-      <c r="M82" t="n">
-        <v>9.19</v>
-      </c>
       <c r="N82" t="n">
+        <v>4.95</v>
+      </c>
+      <c r="O82" t="n">
+        <v>7.77</v>
+      </c>
+      <c r="P82" t="n">
         <v>57.33</v>
       </c>
-      <c r="O82" t="inlineStr">
+      <c r="Q82" t="inlineStr">
         <is>
           <t>Trade-In</t>
         </is>
@@ -5793,39 +6253,45 @@
         </is>
       </c>
       <c r="D83" t="n">
+        <v>90</v>
+      </c>
+      <c r="E83" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="F83" t="n">
         <v>13999.65</v>
       </c>
-      <c r="E83" t="n">
+      <c r="G83" t="n">
         <v>35</v>
       </c>
-      <c r="F83" t="n">
+      <c r="H83" t="n">
         <v>35</v>
       </c>
-      <c r="G83" t="n">
+      <c r="I83" t="n">
         <v>399.99</v>
       </c>
-      <c r="H83" t="n">
+      <c r="J83" t="n">
         <v>0.22</v>
       </c>
-      <c r="I83" t="n">
+      <c r="K83" t="n">
         <v>1.71</v>
       </c>
-      <c r="J83" t="n">
+      <c r="L83" t="n">
         <v>6.08</v>
       </c>
-      <c r="K83" t="n">
+      <c r="M83" t="n">
         <v>0.53</v>
       </c>
-      <c r="L83" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="M83" t="n">
-        <v>2.17</v>
-      </c>
       <c r="N83" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="O83" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="P83" t="n">
         <v>57.14</v>
       </c>
-      <c r="O83" t="inlineStr">
+      <c r="Q83" t="inlineStr">
         <is>
           <t>Kids' Golf Clubs</t>
         </is>
@@ -5848,39 +6314,45 @@
         </is>
       </c>
       <c r="D84" t="n">
+        <v>90</v>
+      </c>
+      <c r="E84" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="F84" t="n">
         <v>13999.6</v>
       </c>
-      <c r="E84" t="n">
+      <c r="G84" t="n">
         <v>40</v>
       </c>
-      <c r="F84" t="n">
+      <c r="H84" t="n">
         <v>40</v>
       </c>
-      <c r="G84" t="n">
+      <c r="I84" t="n">
         <v>349.99</v>
       </c>
-      <c r="H84" t="n">
+      <c r="J84" t="n">
         <v>0.25</v>
       </c>
-      <c r="I84" t="n">
+      <c r="K84" t="n">
         <v>1.82</v>
       </c>
-      <c r="J84" t="n">
+      <c r="L84" t="n">
         <v>6.08</v>
       </c>
-      <c r="K84" t="n">
+      <c r="M84" t="n">
         <v>0.48</v>
       </c>
-      <c r="L84" t="n">
-        <v>2.09</v>
-      </c>
-      <c r="M84" t="n">
-        <v>2.21</v>
-      </c>
       <c r="N84" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="O84" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="P84" t="n">
         <v>62.5</v>
       </c>
-      <c r="O84" t="inlineStr">
+      <c r="Q84" t="inlineStr">
         <is>
           <t>Water Sports</t>
         </is>
@@ -5903,39 +6375,45 @@
         </is>
       </c>
       <c r="D85" t="n">
+        <v>90</v>
+      </c>
+      <c r="E85" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="F85" t="n">
         <v>13649.35</v>
       </c>
-      <c r="E85" t="n">
+      <c r="G85" t="n">
         <v>65</v>
       </c>
-      <c r="F85" t="n">
+      <c r="H85" t="n">
         <v>65</v>
       </c>
-      <c r="G85" t="n">
+      <c r="I85" t="n">
         <v>209.99</v>
       </c>
-      <c r="H85" t="n">
+      <c r="J85" t="n">
         <v>0.4</v>
       </c>
-      <c r="I85" t="n">
+      <c r="K85" t="n">
         <v>1.15</v>
       </c>
-      <c r="J85" t="n">
+      <c r="L85" t="n">
         <v>2.64</v>
       </c>
-      <c r="K85" t="n">
+      <c r="M85" t="n">
         <v>0.51</v>
       </c>
-      <c r="L85" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="M85" t="n">
-        <v>1.56</v>
-      </c>
       <c r="N85" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="O85" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="P85" t="n">
         <v>56.92</v>
       </c>
-      <c r="O85" t="inlineStr">
+      <c r="Q85" t="inlineStr">
         <is>
           <t>Women's Golf Clubs</t>
         </is>
@@ -5958,39 +6436,45 @@
         </is>
       </c>
       <c r="D86" t="n">
+        <v>90</v>
+      </c>
+      <c r="E86" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="F86" t="n">
         <v>13499.46</v>
       </c>
-      <c r="E86" t="n">
+      <c r="G86" t="n">
         <v>54</v>
       </c>
-      <c r="F86" t="n">
+      <c r="H86" t="n">
         <v>54</v>
       </c>
-      <c r="G86" t="n">
+      <c r="I86" t="n">
         <v>249.99</v>
       </c>
-      <c r="H86" t="n">
+      <c r="J86" t="n">
         <v>0.33</v>
       </c>
-      <c r="I86" t="n">
+      <c r="K86" t="n">
         <v>1.22</v>
       </c>
-      <c r="J86" t="n">
+      <c r="L86" t="n">
         <v>2.61</v>
       </c>
-      <c r="K86" t="n">
+      <c r="M86" t="n">
         <v>0.54</v>
       </c>
-      <c r="L86" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="M86" t="n">
-        <v>1.66</v>
-      </c>
       <c r="N86" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="O86" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="P86" t="n">
         <v>64.81</v>
       </c>
-      <c r="O86" t="inlineStr">
+      <c r="Q86" t="inlineStr">
         <is>
           <t>Golf Gloves</t>
         </is>
@@ -6013,39 +6497,45 @@
         </is>
       </c>
       <c r="D87" t="n">
+        <v>90</v>
+      </c>
+      <c r="E87" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="F87" t="n">
         <v>13333</v>
       </c>
-      <c r="E87" t="n">
+      <c r="G87" t="n">
         <v>67</v>
       </c>
-      <c r="F87" t="n">
+      <c r="H87" t="n">
         <v>67</v>
       </c>
-      <c r="G87" t="n">
+      <c r="I87" t="n">
         <v>199</v>
       </c>
-      <c r="H87" t="n">
+      <c r="J87" t="n">
         <v>0.41</v>
       </c>
-      <c r="I87" t="n">
+      <c r="K87" t="n">
         <v>1.25</v>
       </c>
-      <c r="J87" t="n">
+      <c r="L87" t="n">
         <v>2.59</v>
       </c>
-      <c r="K87" t="n">
+      <c r="M87" t="n">
         <v>0.52</v>
       </c>
-      <c r="L87" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="M87" t="n">
-        <v>1.7</v>
-      </c>
       <c r="N87" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="O87" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="P87" t="n">
         <v>62.69</v>
       </c>
-      <c r="O87" t="inlineStr">
+      <c r="Q87" t="inlineStr">
         <is>
           <t>Kids' Golf Clubs</t>
         </is>
@@ -6068,39 +6558,45 @@
         </is>
       </c>
       <c r="D88" t="n">
+        <v>90</v>
+      </c>
+      <c r="E88" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="F88" t="n">
         <v>13311.12</v>
       </c>
-      <c r="E88" t="n">
+      <c r="G88" t="n">
         <v>888</v>
       </c>
-      <c r="F88" t="n">
+      <c r="H88" t="n">
         <v>310</v>
       </c>
-      <c r="G88" t="n">
+      <c r="I88" t="n">
         <v>14.99</v>
       </c>
-      <c r="H88" t="n">
+      <c r="J88" t="n">
         <v>5.48</v>
       </c>
-      <c r="I88" t="n">
+      <c r="K88" t="n">
         <v>5.19</v>
       </c>
-      <c r="J88" t="n">
+      <c r="L88" t="n">
         <v>0.73</v>
       </c>
-      <c r="K88" t="n">
+      <c r="M88" t="n">
         <v>0.53</v>
       </c>
-      <c r="L88" t="n">
-        <v>6.23</v>
-      </c>
-      <c r="M88" t="n">
-        <v>9.130000000000001</v>
-      </c>
       <c r="N88" t="n">
+        <v>4.84</v>
+      </c>
+      <c r="O88" t="n">
+        <v>7.74</v>
+      </c>
+      <c r="P88" t="n">
         <v>55.95</v>
       </c>
-      <c r="O88" t="inlineStr">
+      <c r="Q88" t="inlineStr">
         <is>
           <t>Golf Balls</t>
         </is>
@@ -6123,39 +6619,45 @@
         </is>
       </c>
       <c r="D89" t="n">
+        <v>90</v>
+      </c>
+      <c r="E89" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="F89" t="n">
         <v>12951.36</v>
       </c>
-      <c r="E89" t="n">
+      <c r="G89" t="n">
         <v>864</v>
       </c>
-      <c r="F89" t="n">
+      <c r="H89" t="n">
         <v>282</v>
       </c>
-      <c r="G89" t="n">
+      <c r="I89" t="n">
         <v>14.99</v>
       </c>
-      <c r="H89" t="n">
+      <c r="J89" t="n">
         <v>5.33</v>
       </c>
-      <c r="I89" t="n">
+      <c r="K89" t="n">
         <v>4.89</v>
       </c>
-      <c r="J89" t="n">
+      <c r="L89" t="n">
         <v>0.68</v>
       </c>
-      <c r="K89" t="n">
+      <c r="M89" t="n">
         <v>0.48</v>
       </c>
-      <c r="L89" t="n">
-        <v>5.56</v>
-      </c>
-      <c r="M89" t="n">
-        <v>8.1</v>
-      </c>
       <c r="N89" t="n">
+        <v>4.32</v>
+      </c>
+      <c r="O89" t="n">
+        <v>6.86</v>
+      </c>
+      <c r="P89" t="n">
         <v>56.03</v>
       </c>
-      <c r="O89" t="inlineStr">
+      <c r="Q89" t="inlineStr">
         <is>
           <t>Golf Balls</t>
         </is>
@@ -6178,39 +6680,45 @@
         </is>
       </c>
       <c r="D90" t="n">
+        <v>90</v>
+      </c>
+      <c r="E90" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="F90" t="n">
         <v>12799.68</v>
       </c>
-      <c r="E90" t="n">
+      <c r="G90" t="n">
         <v>32</v>
       </c>
-      <c r="F90" t="n">
+      <c r="H90" t="n">
         <v>32</v>
       </c>
-      <c r="G90" t="n">
+      <c r="I90" t="n">
         <v>399.99</v>
       </c>
-      <c r="H90" t="n">
+      <c r="J90" t="n">
         <v>0.2</v>
       </c>
-      <c r="I90" t="n">
+      <c r="K90" t="n">
         <v>1.45</v>
       </c>
-      <c r="J90" t="n">
+      <c r="L90" t="n">
         <v>6.08</v>
       </c>
-      <c r="K90" t="n">
+      <c r="M90" t="n">
         <v>0.54</v>
       </c>
-      <c r="L90" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="M90" t="n">
-        <v>1.86</v>
-      </c>
       <c r="N90" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="O90" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="P90" t="n">
         <v>65.62</v>
       </c>
-      <c r="O90" t="inlineStr">
+      <c r="Q90" t="inlineStr">
         <is>
           <t>Strength Training</t>
         </is>
@@ -6233,39 +6741,45 @@
         </is>
       </c>
       <c r="D91" t="n">
+        <v>90</v>
+      </c>
+      <c r="E91" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="F91" t="n">
         <v>12599.37</v>
       </c>
-      <c r="E91" t="n">
+      <c r="G91" t="n">
         <v>63</v>
       </c>
-      <c r="F91" t="n">
+      <c r="H91" t="n">
         <v>62</v>
       </c>
-      <c r="G91" t="n">
+      <c r="I91" t="n">
         <v>199.99</v>
       </c>
-      <c r="H91" t="n">
+      <c r="J91" t="n">
         <v>0.39</v>
       </c>
-      <c r="I91" t="n">
+      <c r="K91" t="n">
         <v>1.21</v>
       </c>
-      <c r="J91" t="n">
+      <c r="L91" t="n">
         <v>2.8</v>
       </c>
-      <c r="K91" t="n">
+      <c r="M91" t="n">
         <v>0.49</v>
       </c>
-      <c r="L91" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="M91" t="n">
-        <v>1.58</v>
-      </c>
       <c r="N91" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="O91" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="P91" t="n">
         <v>53.97</v>
       </c>
-      <c r="O91" t="inlineStr">
+      <c r="Q91" t="inlineStr">
         <is>
           <t>Shop By Sport</t>
         </is>
@@ -6284,43 +6798,49 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>Z</t>
         </is>
       </c>
       <c r="D92" t="n">
+        <v>90</v>
+      </c>
+      <c r="E92" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="F92" t="n">
         <v>12587.4</v>
       </c>
-      <c r="E92" t="n">
+      <c r="G92" t="n">
         <v>405</v>
       </c>
-      <c r="F92" t="n">
+      <c r="H92" t="n">
         <v>405</v>
       </c>
-      <c r="G92" t="n">
+      <c r="I92" t="n">
         <v>31.08</v>
       </c>
-      <c r="H92" t="n">
+      <c r="J92" t="n">
         <v>2.5</v>
       </c>
-      <c r="I92" t="n">
+      <c r="K92" t="n">
         <v>25.33</v>
       </c>
-      <c r="J92" t="n">
-        <v>0</v>
-      </c>
-      <c r="K92" t="n">
+      <c r="L92" t="n">
+        <v>4.81</v>
+      </c>
+      <c r="M92" t="n">
         <v>0.48</v>
       </c>
-      <c r="L92" t="n">
-        <v>29.09</v>
-      </c>
-      <c r="M92" t="n">
-        <v>30.3</v>
-      </c>
       <c r="N92" t="n">
+        <v>22.6</v>
+      </c>
+      <c r="O92" t="n">
+        <v>23.81</v>
+      </c>
+      <c r="P92" t="n">
         <v>57.53</v>
       </c>
-      <c r="O92" t="inlineStr">
+      <c r="Q92" t="inlineStr">
         <is>
           <t>Books</t>
         </is>
@@ -6343,39 +6863,45 @@
         </is>
       </c>
       <c r="D93" t="n">
+        <v>90</v>
+      </c>
+      <c r="E93" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="F93" t="n">
         <v>12229.56</v>
       </c>
-      <c r="E93" t="n">
+      <c r="G93" t="n">
         <v>207</v>
       </c>
-      <c r="F93" t="n">
+      <c r="H93" t="n">
         <v>207</v>
       </c>
-      <c r="G93" t="n">
+      <c r="I93" t="n">
         <v>59.08</v>
       </c>
-      <c r="H93" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="I93" t="n">
+      <c r="J93" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="K93" t="n">
         <v>9.5</v>
       </c>
-      <c r="J93" t="n">
+      <c r="L93" t="n">
         <v>4.34</v>
       </c>
-      <c r="K93" t="n">
+      <c r="M93" t="n">
         <v>0.45</v>
       </c>
-      <c r="L93" t="n">
-        <v>10.52</v>
-      </c>
-      <c r="M93" t="n">
-        <v>11.1</v>
-      </c>
       <c r="N93" t="n">
+        <v>8.17</v>
+      </c>
+      <c r="O93" t="n">
+        <v>8.75</v>
+      </c>
+      <c r="P93" t="n">
         <v>54.59</v>
       </c>
-      <c r="O93" t="inlineStr">
+      <c r="Q93" t="inlineStr">
         <is>
           <t>Baby</t>
         </is>
@@ -6398,39 +6924,45 @@
         </is>
       </c>
       <c r="D94" t="n">
+        <v>90</v>
+      </c>
+      <c r="E94" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="F94" t="n">
         <v>12096</v>
       </c>
-      <c r="E94" t="n">
+      <c r="G94" t="n">
         <v>64</v>
       </c>
-      <c r="F94" t="n">
+      <c r="H94" t="n">
         <v>64</v>
       </c>
-      <c r="G94" t="n">
+      <c r="I94" t="n">
         <v>189</v>
       </c>
-      <c r="H94" t="n">
+      <c r="J94" t="n">
         <v>0.4</v>
       </c>
-      <c r="I94" t="n">
+      <c r="K94" t="n">
         <v>1.21</v>
       </c>
-      <c r="J94" t="n">
+      <c r="L94" t="n">
         <v>2.76</v>
       </c>
-      <c r="K94" t="n">
+      <c r="M94" t="n">
         <v>0.54</v>
       </c>
-      <c r="L94" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="M94" t="n">
-        <v>1.69</v>
-      </c>
       <c r="N94" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="O94" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="P94" t="n">
         <v>60.94</v>
       </c>
-      <c r="O94" t="inlineStr">
+      <c r="Q94" t="inlineStr">
         <is>
           <t>Strength Training</t>
         </is>
@@ -6453,39 +6985,45 @@
         </is>
       </c>
       <c r="D95" t="n">
+        <v>90</v>
+      </c>
+      <c r="E95" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="F95" t="n">
         <v>11799.41</v>
       </c>
-      <c r="E95" t="n">
+      <c r="G95" t="n">
         <v>59</v>
       </c>
-      <c r="F95" t="n">
+      <c r="H95" t="n">
         <v>59</v>
       </c>
-      <c r="G95" t="n">
+      <c r="I95" t="n">
         <v>199.99</v>
       </c>
-      <c r="H95" t="n">
+      <c r="J95" t="n">
         <v>0.36</v>
       </c>
-      <c r="I95" t="n">
+      <c r="K95" t="n">
         <v>1.06</v>
       </c>
-      <c r="J95" t="n">
+      <c r="L95" t="n">
         <v>2.6</v>
       </c>
-      <c r="K95" t="n">
+      <c r="M95" t="n">
         <v>0.53</v>
       </c>
-      <c r="L95" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="M95" t="n">
-        <v>1.46</v>
-      </c>
       <c r="N95" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="O95" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="P95" t="n">
         <v>55.93</v>
       </c>
-      <c r="O95" t="inlineStr">
+      <c r="Q95" t="inlineStr">
         <is>
           <t>Kids' Golf Clubs</t>
         </is>
@@ -6508,39 +7046,45 @@
         </is>
       </c>
       <c r="D96" t="n">
+        <v>90</v>
+      </c>
+      <c r="E96" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="F96" t="n">
         <v>11699.35</v>
       </c>
-      <c r="E96" t="n">
+      <c r="G96" t="n">
         <v>65</v>
       </c>
-      <c r="F96" t="n">
+      <c r="H96" t="n">
         <v>65</v>
       </c>
-      <c r="G96" t="n">
+      <c r="I96" t="n">
         <v>179.99</v>
       </c>
-      <c r="H96" t="n">
+      <c r="J96" t="n">
         <v>0.4</v>
       </c>
-      <c r="I96" t="n">
+      <c r="K96" t="n">
         <v>1.2</v>
       </c>
-      <c r="J96" t="n">
+      <c r="L96" t="n">
         <v>2.61</v>
       </c>
-      <c r="K96" t="n">
+      <c r="M96" t="n">
         <v>0.51</v>
       </c>
-      <c r="L96" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="M96" t="n">
-        <v>1.62</v>
-      </c>
       <c r="N96" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="O96" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="P96" t="n">
         <v>58.46</v>
       </c>
-      <c r="O96" t="inlineStr">
+      <c r="Q96" t="inlineStr">
         <is>
           <t>Golf Gloves</t>
         </is>
@@ -6563,39 +7107,45 @@
         </is>
       </c>
       <c r="D97" t="n">
+        <v>90</v>
+      </c>
+      <c r="E97" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="F97" t="n">
         <v>11598.55</v>
       </c>
-      <c r="E97" t="n">
+      <c r="G97" t="n">
         <v>145</v>
       </c>
-      <c r="F97" t="n">
+      <c r="H97" t="n">
         <v>53</v>
       </c>
-      <c r="G97" t="n">
+      <c r="I97" t="n">
         <v>79.98999999999999</v>
       </c>
-      <c r="H97" t="n">
+      <c r="J97" t="n">
         <v>0.9</v>
       </c>
-      <c r="I97" t="n">
+      <c r="K97" t="n">
         <v>2.82</v>
       </c>
-      <c r="J97" t="n">
+      <c r="L97" t="n">
         <v>2.99</v>
       </c>
-      <c r="K97" t="n">
+      <c r="M97" t="n">
         <v>0.48</v>
       </c>
-      <c r="L97" t="n">
-        <v>3.22</v>
-      </c>
-      <c r="M97" t="n">
-        <v>3.65</v>
-      </c>
       <c r="N97" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="O97" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="P97" t="n">
         <v>54.72</v>
       </c>
-      <c r="O97" t="inlineStr">
+      <c r="Q97" t="inlineStr">
         <is>
           <t>Women's Golf Clubs</t>
         </is>
@@ -6618,39 +7168,45 @@
         </is>
       </c>
       <c r="D98" t="n">
+        <v>90</v>
+      </c>
+      <c r="E98" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="F98" t="n">
         <v>10799.64</v>
       </c>
-      <c r="E98" t="n">
+      <c r="G98" t="n">
         <v>36</v>
       </c>
-      <c r="F98" t="n">
+      <c r="H98" t="n">
         <v>35</v>
       </c>
-      <c r="G98" t="n">
+      <c r="I98" t="n">
         <v>299.99</v>
       </c>
-      <c r="H98" t="n">
+      <c r="J98" t="n">
         <v>0.22</v>
       </c>
-      <c r="I98" t="n">
+      <c r="K98" t="n">
         <v>1.74</v>
       </c>
-      <c r="J98" t="n">
+      <c r="L98" t="n">
         <v>6.08</v>
       </c>
-      <c r="K98" t="n">
+      <c r="M98" t="n">
         <v>0.52</v>
       </c>
-      <c r="L98" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="M98" t="n">
-        <v>2.18</v>
-      </c>
       <c r="N98" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="O98" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="P98" t="n">
         <v>63.89</v>
       </c>
-      <c r="O98" t="inlineStr">
+      <c r="Q98" t="inlineStr">
         <is>
           <t>Cleats</t>
         </is>
@@ -6673,39 +7229,45 @@
         </is>
       </c>
       <c r="D99" t="n">
+        <v>90</v>
+      </c>
+      <c r="E99" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="F99" t="n">
         <v>10799.64</v>
       </c>
-      <c r="E99" t="n">
+      <c r="G99" t="n">
         <v>36</v>
       </c>
-      <c r="F99" t="n">
+      <c r="H99" t="n">
         <v>34</v>
       </c>
-      <c r="G99" t="n">
+      <c r="I99" t="n">
         <v>299.99</v>
       </c>
-      <c r="H99" t="n">
+      <c r="J99" t="n">
         <v>0.22</v>
       </c>
-      <c r="I99" t="n">
+      <c r="K99" t="n">
         <v>1.65</v>
       </c>
-      <c r="J99" t="n">
+      <c r="L99" t="n">
         <v>6.08</v>
       </c>
-      <c r="K99" t="n">
+      <c r="M99" t="n">
         <v>0.54</v>
       </c>
-      <c r="L99" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="M99" t="n">
-        <v>2.13</v>
-      </c>
       <c r="N99" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="O99" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="P99" t="n">
         <v>66.67</v>
       </c>
-      <c r="O99" t="inlineStr">
+      <c r="Q99" t="inlineStr">
         <is>
           <t>Kids' Golf Clubs</t>
         </is>
@@ -6728,39 +7290,45 @@
         </is>
       </c>
       <c r="D100" t="n">
+        <v>90</v>
+      </c>
+      <c r="E100" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="F100" t="n">
         <v>10399.35</v>
       </c>
-      <c r="E100" t="n">
+      <c r="G100" t="n">
         <v>65</v>
       </c>
-      <c r="F100" t="n">
+      <c r="H100" t="n">
         <v>65</v>
       </c>
-      <c r="G100" t="n">
+      <c r="I100" t="n">
         <v>159.99</v>
       </c>
-      <c r="H100" t="n">
+      <c r="J100" t="n">
         <v>0.4</v>
       </c>
-      <c r="I100" t="n">
+      <c r="K100" t="n">
         <v>1.15</v>
       </c>
-      <c r="J100" t="n">
+      <c r="L100" t="n">
         <v>2.5</v>
       </c>
-      <c r="K100" t="n">
+      <c r="M100" t="n">
         <v>0.48</v>
       </c>
-      <c r="L100" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="M100" t="n">
-        <v>1.5</v>
-      </c>
       <c r="N100" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="O100" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="P100" t="n">
         <v>56.92</v>
       </c>
-      <c r="O100" t="inlineStr">
+      <c r="Q100" t="inlineStr">
         <is>
           <t>Baseball &amp; Softball</t>
         </is>
@@ -6783,39 +7351,45 @@
         </is>
       </c>
       <c r="D101" t="n">
+        <v>90</v>
+      </c>
+      <c r="E101" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="F101" t="n">
         <v>10369.39</v>
       </c>
-      <c r="E101" t="n">
+      <c r="G101" t="n">
         <v>61</v>
       </c>
-      <c r="F101" t="n">
+      <c r="H101" t="n">
         <v>61</v>
       </c>
-      <c r="G101" t="n">
+      <c r="I101" t="n">
         <v>169.99</v>
       </c>
-      <c r="H101" t="n">
+      <c r="J101" t="n">
         <v>0.38</v>
       </c>
-      <c r="I101" t="n">
+      <c r="K101" t="n">
         <v>1.18</v>
       </c>
-      <c r="J101" t="n">
+      <c r="L101" t="n">
         <v>2.79</v>
       </c>
-      <c r="K101" t="n">
+      <c r="M101" t="n">
         <v>0.48</v>
       </c>
-      <c r="L101" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="M101" t="n">
-        <v>1.52</v>
-      </c>
       <c r="N101" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="O101" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="P101" t="n">
         <v>68.84999999999999</v>
       </c>
-      <c r="O101" t="inlineStr">
+      <c r="Q101" t="inlineStr">
         <is>
           <t>Golf Bags &amp; Carts</t>
         </is>
@@ -6838,39 +7412,45 @@
         </is>
       </c>
       <c r="D102" t="n">
+        <v>90</v>
+      </c>
+      <c r="E102" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="F102" t="n">
         <v>10199.66</v>
       </c>
-      <c r="E102" t="n">
+      <c r="G102" t="n">
         <v>34</v>
       </c>
-      <c r="F102" t="n">
+      <c r="H102" t="n">
         <v>34</v>
       </c>
-      <c r="G102" t="n">
+      <c r="I102" t="n">
         <v>299.99</v>
       </c>
-      <c r="H102" t="n">
+      <c r="J102" t="n">
         <v>0.21</v>
       </c>
-      <c r="I102" t="n">
+      <c r="K102" t="n">
         <v>1.54</v>
       </c>
-      <c r="J102" t="n">
+      <c r="L102" t="n">
         <v>6.08</v>
       </c>
-      <c r="K102" t="n">
+      <c r="M102" t="n">
         <v>0.54</v>
       </c>
-      <c r="L102" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="M102" t="n">
-        <v>1.98</v>
-      </c>
       <c r="N102" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="O102" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="P102" t="n">
         <v>64.70999999999999</v>
       </c>
-      <c r="O102" t="inlineStr">
+      <c r="Q102" t="inlineStr">
         <is>
           <t>Golf Gloves</t>
         </is>
@@ -6893,39 +7473,45 @@
         </is>
       </c>
       <c r="D103" t="n">
+        <v>90</v>
+      </c>
+      <c r="E103" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="F103" t="n">
         <v>9999.9</v>
       </c>
-      <c r="E103" t="n">
+      <c r="G103" t="n">
         <v>10</v>
       </c>
-      <c r="F103" t="n">
+      <c r="H103" t="n">
         <v>10</v>
       </c>
-      <c r="G103" t="n">
+      <c r="I103" t="n">
         <v>999.99</v>
       </c>
-      <c r="H103" t="n">
+      <c r="J103" t="n">
         <v>0.06</v>
       </c>
-      <c r="I103" t="n">
+      <c r="K103" t="n">
         <v>0.6</v>
       </c>
-      <c r="J103" t="n">
+      <c r="L103" t="n">
         <v>4.98</v>
       </c>
-      <c r="K103" t="n">
+      <c r="M103" t="n">
         <v>0.57</v>
       </c>
-      <c r="L103" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="M103" t="n">
-        <v>0.78</v>
-      </c>
       <c r="N103" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="O103" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="P103" t="n">
         <v>70</v>
       </c>
-      <c r="O103" t="inlineStr">
+      <c r="Q103" t="inlineStr">
         <is>
           <t>Basketball</t>
         </is>
@@ -6948,39 +7534,45 @@
         </is>
       </c>
       <c r="D104" t="n">
+        <v>90</v>
+      </c>
+      <c r="E104" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="F104" t="n">
         <v>9449.299999999999</v>
       </c>
-      <c r="E104" t="n">
+      <c r="G104" t="n">
         <v>70</v>
       </c>
-      <c r="F104" t="n">
+      <c r="H104" t="n">
         <v>69</v>
       </c>
-      <c r="G104" t="n">
+      <c r="I104" t="n">
         <v>134.99</v>
       </c>
-      <c r="H104" t="n">
+      <c r="J104" t="n">
         <v>0.43</v>
       </c>
-      <c r="I104" t="n">
+      <c r="K104" t="n">
         <v>1.29</v>
       </c>
-      <c r="J104" t="n">
+      <c r="L104" t="n">
         <v>2.83</v>
       </c>
-      <c r="K104" t="n">
+      <c r="M104" t="n">
         <v>0.47</v>
       </c>
-      <c r="L104" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="M104" t="n">
-        <v>1.66</v>
-      </c>
       <c r="N104" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="O104" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="P104" t="n">
         <v>50</v>
       </c>
-      <c r="O104" t="inlineStr">
+      <c r="Q104" t="inlineStr">
         <is>
           <t>Men's Golf Clubs</t>
         </is>
@@ -7003,39 +7595,45 @@
         </is>
       </c>
       <c r="D105" t="n">
+        <v>90</v>
+      </c>
+      <c r="E105" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="F105" t="n">
         <v>9349.15</v>
       </c>
-      <c r="E105" t="n">
+      <c r="G105" t="n">
         <v>85</v>
       </c>
-      <c r="F105" t="n">
+      <c r="H105" t="n">
         <v>85</v>
       </c>
-      <c r="G105" t="n">
+      <c r="I105" t="n">
         <v>109.99</v>
       </c>
-      <c r="H105" t="n">
+      <c r="J105" t="n">
         <v>0.52</v>
       </c>
-      <c r="I105" t="n">
+      <c r="K105" t="n">
         <v>1.47</v>
       </c>
-      <c r="J105" t="n">
+      <c r="L105" t="n">
         <v>2.63</v>
       </c>
-      <c r="K105" t="n">
+      <c r="M105" t="n">
         <v>0.5</v>
       </c>
-      <c r="L105" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="M105" t="n">
-        <v>1.97</v>
-      </c>
       <c r="N105" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="O105" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="P105" t="n">
         <v>50.59</v>
       </c>
-      <c r="O105" t="inlineStr">
+      <c r="Q105" t="inlineStr">
         <is>
           <t>Men's Golf Clubs</t>
         </is>
@@ -7058,39 +7656,45 @@
         </is>
       </c>
       <c r="D106" t="n">
+        <v>90</v>
+      </c>
+      <c r="E106" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="F106" t="n">
         <v>8999.4</v>
       </c>
-      <c r="E106" t="n">
+      <c r="G106" t="n">
         <v>60</v>
       </c>
-      <c r="F106" t="n">
+      <c r="H106" t="n">
         <v>59</v>
       </c>
-      <c r="G106" t="n">
+      <c r="I106" t="n">
         <v>149.99</v>
       </c>
-      <c r="H106" t="n">
+      <c r="J106" t="n">
         <v>0.37</v>
       </c>
-      <c r="I106" t="n">
+      <c r="K106" t="n">
         <v>1.15</v>
       </c>
-      <c r="J106" t="n">
+      <c r="L106" t="n">
         <v>2.7</v>
       </c>
-      <c r="K106" t="n">
+      <c r="M106" t="n">
         <v>0.46</v>
       </c>
-      <c r="L106" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="M106" t="n">
-        <v>1.46</v>
-      </c>
       <c r="N106" t="n">
+        <v>1</v>
+      </c>
+      <c r="O106" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="P106" t="n">
         <v>50</v>
       </c>
-      <c r="O106" t="inlineStr">
+      <c r="Q106" t="inlineStr">
         <is>
           <t>Hunting &amp; Shooting</t>
         </is>
@@ -7113,39 +7717,45 @@
         </is>
       </c>
       <c r="D107" t="n">
+        <v>90</v>
+      </c>
+      <c r="E107" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="F107" t="n">
         <v>8909.73</v>
       </c>
-      <c r="E107" t="n">
+      <c r="G107" t="n">
         <v>27</v>
       </c>
-      <c r="F107" t="n">
+      <c r="H107" t="n">
         <v>25</v>
       </c>
-      <c r="G107" t="n">
+      <c r="I107" t="n">
         <v>329.99</v>
       </c>
-      <c r="H107" t="n">
+      <c r="J107" t="n">
         <v>0.17</v>
       </c>
-      <c r="I107" t="n">
+      <c r="K107" t="n">
         <v>1.23</v>
       </c>
-      <c r="J107" t="n">
+      <c r="L107" t="n">
         <v>6.08</v>
       </c>
-      <c r="K107" t="n">
+      <c r="M107" t="n">
         <v>0.49</v>
       </c>
-      <c r="L107" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="M107" t="n">
-        <v>1.5</v>
-      </c>
       <c r="N107" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="O107" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="P107" t="n">
         <v>51.85</v>
       </c>
-      <c r="O107" t="inlineStr">
+      <c r="Q107" t="inlineStr">
         <is>
           <t>Hockey</t>
         </is>
@@ -7168,39 +7778,45 @@
         </is>
       </c>
       <c r="D108" t="n">
+        <v>90</v>
+      </c>
+      <c r="E108" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="F108" t="n">
         <v>8871.120000000001</v>
       </c>
-      <c r="E108" t="n">
+      <c r="G108" t="n">
         <v>888</v>
       </c>
-      <c r="F108" t="n">
+      <c r="H108" t="n">
         <v>284</v>
       </c>
-      <c r="G108" t="n">
+      <c r="I108" t="n">
         <v>9.99</v>
       </c>
-      <c r="H108" t="n">
+      <c r="J108" t="n">
         <v>5.48</v>
       </c>
-      <c r="I108" t="n">
+      <c r="K108" t="n">
         <v>5.27</v>
       </c>
-      <c r="J108" t="n">
+      <c r="L108" t="n">
         <v>0.68</v>
       </c>
-      <c r="K108" t="n">
+      <c r="M108" t="n">
         <v>0.51</v>
       </c>
-      <c r="L108" t="n">
-        <v>6.22</v>
-      </c>
-      <c r="M108" t="n">
-        <v>9.02</v>
-      </c>
       <c r="N108" t="n">
+        <v>4.83</v>
+      </c>
+      <c r="O108" t="n">
+        <v>7.63</v>
+      </c>
+      <c r="P108" t="n">
         <v>55.79</v>
       </c>
-      <c r="O108" t="inlineStr">
+      <c r="Q108" t="inlineStr">
         <is>
           <t>Golf Gloves</t>
         </is>
@@ -7223,39 +7839,45 @@
         </is>
       </c>
       <c r="D109" t="n">
+        <v>90</v>
+      </c>
+      <c r="E109" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="F109" t="n">
         <v>8839.32</v>
       </c>
-      <c r="E109" t="n">
+      <c r="G109" t="n">
         <v>68</v>
       </c>
-      <c r="F109" t="n">
+      <c r="H109" t="n">
         <v>68</v>
       </c>
-      <c r="G109" t="n">
+      <c r="I109" t="n">
         <v>129.99</v>
       </c>
-      <c r="H109" t="n">
+      <c r="J109" t="n">
         <v>0.42</v>
       </c>
-      <c r="I109" t="n">
+      <c r="K109" t="n">
         <v>1.35</v>
       </c>
-      <c r="J109" t="n">
+      <c r="L109" t="n">
         <v>2.82</v>
       </c>
-      <c r="K109" t="n">
+      <c r="M109" t="n">
         <v>0.47</v>
       </c>
-      <c r="L109" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="M109" t="n">
-        <v>1.72</v>
-      </c>
       <c r="N109" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="O109" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="P109" t="n">
         <v>45.59</v>
       </c>
-      <c r="O109" t="inlineStr">
+      <c r="Q109" t="inlineStr">
         <is>
           <t>Golf Apparel</t>
         </is>
@@ -7278,39 +7900,45 @@
         </is>
       </c>
       <c r="D110" t="n">
+        <v>90</v>
+      </c>
+      <c r="E110" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="F110" t="n">
         <v>8699.709999999999</v>
       </c>
-      <c r="E110" t="n">
+      <c r="G110" t="n">
         <v>29</v>
       </c>
-      <c r="F110" t="n">
+      <c r="H110" t="n">
         <v>28</v>
       </c>
-      <c r="G110" t="n">
+      <c r="I110" t="n">
         <v>299.99</v>
       </c>
-      <c r="H110" t="n">
+      <c r="J110" t="n">
         <v>0.18</v>
       </c>
-      <c r="I110" t="n">
+      <c r="K110" t="n">
         <v>1.38</v>
       </c>
-      <c r="J110" t="n">
+      <c r="L110" t="n">
         <v>6.08</v>
       </c>
-      <c r="K110" t="n">
+      <c r="M110" t="n">
         <v>0.52</v>
       </c>
-      <c r="L110" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="M110" t="n">
-        <v>1.74</v>
-      </c>
       <c r="N110" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="O110" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="P110" t="n">
         <v>65.52</v>
       </c>
-      <c r="O110" t="inlineStr">
+      <c r="Q110" t="inlineStr">
         <is>
           <t>Basketball</t>
         </is>
@@ -7333,39 +7961,45 @@
         </is>
       </c>
       <c r="D111" t="n">
+        <v>90</v>
+      </c>
+      <c r="E111" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="F111" t="n">
         <v>8399.719999999999</v>
       </c>
-      <c r="E111" t="n">
+      <c r="G111" t="n">
         <v>28</v>
       </c>
-      <c r="F111" t="n">
+      <c r="H111" t="n">
         <v>27</v>
       </c>
-      <c r="G111" t="n">
+      <c r="I111" t="n">
         <v>299.99</v>
       </c>
-      <c r="H111" t="n">
+      <c r="J111" t="n">
         <v>0.17</v>
       </c>
-      <c r="I111" t="n">
+      <c r="K111" t="n">
         <v>1.27</v>
       </c>
-      <c r="J111" t="n">
+      <c r="L111" t="n">
         <v>6.08</v>
       </c>
-      <c r="K111" t="n">
+      <c r="M111" t="n">
         <v>0.44</v>
       </c>
-      <c r="L111" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="M111" t="n">
-        <v>1.46</v>
-      </c>
       <c r="N111" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="O111" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="P111" t="n">
         <v>50</v>
       </c>
-      <c r="O111" t="inlineStr">
+      <c r="Q111" t="inlineStr">
         <is>
           <t>Basketball</t>
         </is>
@@ -7388,39 +8022,45 @@
         </is>
       </c>
       <c r="D112" t="n">
+        <v>90</v>
+      </c>
+      <c r="E112" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="F112" t="n">
         <v>8399.299999999999</v>
       </c>
-      <c r="E112" t="n">
+      <c r="G112" t="n">
         <v>70</v>
       </c>
-      <c r="F112" t="n">
+      <c r="H112" t="n">
         <v>70</v>
       </c>
-      <c r="G112" t="n">
+      <c r="I112" t="n">
         <v>119.99</v>
       </c>
-      <c r="H112" t="n">
+      <c r="J112" t="n">
         <v>0.43</v>
       </c>
-      <c r="I112" t="n">
+      <c r="K112" t="n">
         <v>1.3</v>
       </c>
-      <c r="J112" t="n">
+      <c r="L112" t="n">
         <v>2.56</v>
       </c>
-      <c r="K112" t="n">
+      <c r="M112" t="n">
         <v>0.51</v>
       </c>
-      <c r="L112" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="M112" t="n">
-        <v>1.75</v>
-      </c>
       <c r="N112" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="O112" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="P112" t="n">
         <v>51.43</v>
       </c>
-      <c r="O112" t="inlineStr">
+      <c r="Q112" t="inlineStr">
         <is>
           <t>Golf Apparel</t>
         </is>
@@ -7443,39 +8083,45 @@
         </is>
       </c>
       <c r="D113" t="n">
+        <v>90</v>
+      </c>
+      <c r="E113" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="F113" t="n">
         <v>8208</v>
       </c>
-      <c r="E113" t="n">
+      <c r="G113" t="n">
         <v>76</v>
       </c>
-      <c r="F113" t="n">
+      <c r="H113" t="n">
         <v>76</v>
       </c>
-      <c r="G113" t="n">
+      <c r="I113" t="n">
         <v>108</v>
       </c>
-      <c r="H113" t="n">
+      <c r="J113" t="n">
         <v>0.47</v>
       </c>
-      <c r="I113" t="n">
+      <c r="K113" t="n">
         <v>1.39</v>
       </c>
-      <c r="J113" t="n">
+      <c r="L113" t="n">
         <v>2.61</v>
       </c>
-      <c r="K113" t="n">
+      <c r="M113" t="n">
         <v>0.47</v>
       </c>
-      <c r="L113" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="M113" t="n">
-        <v>1.79</v>
-      </c>
       <c r="N113" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="O113" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="P113" t="n">
         <v>60.53</v>
       </c>
-      <c r="O113" t="inlineStr">
+      <c r="Q113" t="inlineStr">
         <is>
           <t>Golf Shoes</t>
         </is>
@@ -7498,39 +8144,45 @@
         </is>
       </c>
       <c r="D114" t="n">
+        <v>90</v>
+      </c>
+      <c r="E114" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="F114" t="n">
         <v>7999.36</v>
       </c>
-      <c r="E114" t="n">
+      <c r="G114" t="n">
         <v>64</v>
       </c>
-      <c r="F114" t="n">
+      <c r="H114" t="n">
         <v>63</v>
       </c>
-      <c r="G114" t="n">
+      <c r="I114" t="n">
         <v>124.99</v>
       </c>
-      <c r="H114" t="n">
+      <c r="J114" t="n">
         <v>0.4</v>
       </c>
-      <c r="I114" t="n">
+      <c r="K114" t="n">
         <v>1.2</v>
       </c>
-      <c r="J114" t="n">
+      <c r="L114" t="n">
         <v>2.66</v>
       </c>
-      <c r="K114" t="n">
+      <c r="M114" t="n">
         <v>0.5600000000000001</v>
       </c>
-      <c r="L114" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="M114" t="n">
-        <v>1.7</v>
-      </c>
       <c r="N114" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="O114" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="P114" t="n">
         <v>60.94</v>
       </c>
-      <c r="O114" t="inlineStr">
+      <c r="Q114" t="inlineStr">
         <is>
           <t>Soccer</t>
         </is>
@@ -7553,39 +8205,45 @@
         </is>
       </c>
       <c r="D115" t="n">
+        <v>90</v>
+      </c>
+      <c r="E115" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="F115" t="n">
         <v>7539.42</v>
       </c>
-      <c r="E115" t="n">
+      <c r="G115" t="n">
         <v>58</v>
       </c>
-      <c r="F115" t="n">
+      <c r="H115" t="n">
         <v>58</v>
       </c>
-      <c r="G115" t="n">
+      <c r="I115" t="n">
         <v>129.99</v>
       </c>
-      <c r="H115" t="n">
+      <c r="J115" t="n">
         <v>0.36</v>
       </c>
-      <c r="I115" t="n">
+      <c r="K115" t="n">
         <v>1.06</v>
       </c>
-      <c r="J115" t="n">
+      <c r="L115" t="n">
         <v>2.69</v>
       </c>
-      <c r="K115" t="n">
+      <c r="M115" t="n">
         <v>0.45</v>
       </c>
-      <c r="L115" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="M115" t="n">
-        <v>1.34</v>
-      </c>
       <c r="N115" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="O115" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="P115" t="n">
         <v>46.55</v>
       </c>
-      <c r="O115" t="inlineStr">
+      <c r="Q115" t="inlineStr">
         <is>
           <t>Men's Golf Clubs</t>
         </is>
@@ -7608,39 +8266,45 @@
         </is>
       </c>
       <c r="D116" t="n">
+        <v>90</v>
+      </c>
+      <c r="E116" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="F116" t="n">
         <v>6599.89</v>
       </c>
-      <c r="E116" t="n">
+      <c r="G116" t="n">
         <v>11</v>
       </c>
-      <c r="F116" t="n">
+      <c r="H116" t="n">
         <v>8</v>
       </c>
-      <c r="G116" t="n">
+      <c r="I116" t="n">
         <v>599.99</v>
       </c>
-      <c r="H116" t="n">
+      <c r="J116" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="I116" t="n">
+      <c r="K116" t="n">
         <v>0.79</v>
       </c>
-      <c r="J116" t="n">
+      <c r="L116" t="n">
         <v>4.4</v>
       </c>
-      <c r="K116" t="n">
+      <c r="M116" t="n">
         <v>0.48</v>
       </c>
-      <c r="L116" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="M116" t="n">
-        <v>0.93</v>
-      </c>
       <c r="N116" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="O116" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="P116" t="n">
         <v>54.55</v>
       </c>
-      <c r="O116" t="inlineStr">
+      <c r="Q116" t="inlineStr">
         <is>
           <t>Kids' Golf Clubs</t>
         </is>
@@ -7659,43 +8323,49 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>Z</t>
         </is>
       </c>
       <c r="D117" t="n">
+        <v>90</v>
+      </c>
+      <c r="E117" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="F117" t="n">
         <v>6104.66</v>
       </c>
-      <c r="E117" t="n">
+      <c r="G117" t="n">
         <v>529</v>
       </c>
-      <c r="F117" t="n">
+      <c r="H117" t="n">
         <v>529</v>
       </c>
-      <c r="G117" t="n">
+      <c r="I117" t="n">
         <v>11.54</v>
       </c>
-      <c r="H117" t="n">
+      <c r="J117" t="n">
         <v>3.27</v>
       </c>
-      <c r="I117" t="n">
+      <c r="K117" t="n">
         <v>25.26</v>
       </c>
-      <c r="J117" t="n">
-        <v>0</v>
-      </c>
-      <c r="K117" t="n">
+      <c r="L117" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="M117" t="n">
         <v>0.5</v>
       </c>
-      <c r="L117" t="n">
-        <v>29.56</v>
-      </c>
-      <c r="M117" t="n">
-        <v>31.2</v>
-      </c>
       <c r="N117" t="n">
+        <v>22.96</v>
+      </c>
+      <c r="O117" t="n">
+        <v>24.6</v>
+      </c>
+      <c r="P117" t="n">
         <v>58.41</v>
       </c>
-      <c r="O117" t="inlineStr">
+      <c r="Q117" t="inlineStr">
         <is>
           <t>Toys</t>
         </is>
@@ -7718,39 +8388,45 @@
         </is>
       </c>
       <c r="D118" t="n">
+        <v>90</v>
+      </c>
+      <c r="E118" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="F118" t="n">
         <v>5999.9</v>
       </c>
-      <c r="E118" t="n">
+      <c r="G118" t="n">
         <v>10</v>
       </c>
-      <c r="F118" t="n">
+      <c r="H118" t="n">
         <v>10</v>
       </c>
-      <c r="G118" t="n">
+      <c r="I118" t="n">
         <v>599.99</v>
       </c>
-      <c r="H118" t="n">
+      <c r="J118" t="n">
         <v>0.06</v>
       </c>
-      <c r="I118" t="n">
+      <c r="K118" t="n">
         <v>0.79</v>
       </c>
-      <c r="J118" t="n">
+      <c r="L118" t="n">
         <v>4.59</v>
       </c>
-      <c r="K118" t="n">
+      <c r="M118" t="n">
         <v>0.5</v>
       </c>
-      <c r="L118" t="n">
-        <v>0.92</v>
-      </c>
-      <c r="M118" t="n">
-        <v>0.95</v>
-      </c>
       <c r="N118" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="O118" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="P118" t="n">
         <v>60</v>
       </c>
-      <c r="O118" t="inlineStr">
+      <c r="Q118" t="inlineStr">
         <is>
           <t>Fitness Accessories</t>
         </is>
@@ -7773,39 +8449,45 @@
         </is>
       </c>
       <c r="D119" t="n">
+        <v>90</v>
+      </c>
+      <c r="E119" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="F119" t="n">
         <v>5937.3</v>
       </c>
-      <c r="E119" t="n">
+      <c r="G119" t="n">
         <v>54</v>
       </c>
-      <c r="F119" t="n">
+      <c r="H119" t="n">
         <v>53</v>
       </c>
-      <c r="G119" t="n">
+      <c r="I119" t="n">
         <v>109.95</v>
       </c>
-      <c r="H119" t="n">
+      <c r="J119" t="n">
         <v>0.33</v>
       </c>
-      <c r="I119" t="n">
+      <c r="K119" t="n">
         <v>1.05</v>
       </c>
-      <c r="J119" t="n">
+      <c r="L119" t="n">
         <v>2.52</v>
       </c>
-      <c r="K119" t="n">
+      <c r="M119" t="n">
         <v>0.54</v>
       </c>
-      <c r="L119" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="M119" t="n">
-        <v>1.45</v>
-      </c>
       <c r="N119" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="O119" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="P119" t="n">
         <v>53.7</v>
       </c>
-      <c r="O119" t="inlineStr">
+      <c r="Q119" t="inlineStr">
         <is>
           <t>Kids' Golf Clubs</t>
         </is>
@@ -7828,39 +8510,45 @@
         </is>
       </c>
       <c r="D120" t="n">
+        <v>90</v>
+      </c>
+      <c r="E120" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="F120" t="n">
         <v>3059.59</v>
       </c>
-      <c r="E120" t="n">
+      <c r="G120" t="n">
         <v>271</v>
       </c>
-      <c r="F120" t="n">
+      <c r="H120" t="n">
         <v>271</v>
       </c>
-      <c r="G120" t="n">
+      <c r="I120" t="n">
         <v>11.29</v>
       </c>
-      <c r="H120" t="n">
+      <c r="J120" t="n">
         <v>1.67</v>
       </c>
-      <c r="I120" t="n">
+      <c r="K120" t="n">
         <v>13.13</v>
       </c>
-      <c r="J120" t="n">
+      <c r="L120" t="n">
         <v>4.24</v>
       </c>
-      <c r="K120" t="n">
+      <c r="M120" t="n">
         <v>0.49</v>
       </c>
-      <c r="L120" t="n">
-        <v>15.21</v>
-      </c>
-      <c r="M120" t="n">
-        <v>16.03</v>
-      </c>
       <c r="N120" t="n">
+        <v>11.82</v>
+      </c>
+      <c r="O120" t="n">
+        <v>12.64</v>
+      </c>
+      <c r="P120" t="n">
         <v>54.24</v>
       </c>
-      <c r="O120" t="inlineStr">
+      <c r="Q120" t="inlineStr">
         <is>
           <t>CDs</t>
         </is>
